--- a/salidas/empresas/WFC.xlsx
+++ b/salidas/empresas/WFC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -420,24 +432,6784 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:I250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nota</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>precio_ajustado</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>precio_cierre</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>volumen</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>eps_ttm</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pe</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acciones_circulacion</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sin precios de Yahoo; ver hoja Info</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>38748</v>
+      </c>
+      <c r="B2" t="n">
+        <v>17.76022720336914</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31.18000030517578</v>
+      </c>
+      <c r="D2" t="n">
+        <v>184370400</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>38776</v>
+      </c>
+      <c r="B3" t="n">
+        <v>18.43801307678223</v>
+      </c>
+      <c r="C3" t="n">
+        <v>32.09999847412109</v>
+      </c>
+      <c r="D3" t="n">
+        <v>146283200</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>38807</v>
+      </c>
+      <c r="B4" t="n">
+        <v>18.34323501586914</v>
+      </c>
+      <c r="C4" t="n">
+        <v>31.93499946594238</v>
+      </c>
+      <c r="D4" t="n">
+        <v>167321200</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>38837</v>
+      </c>
+      <c r="B5" t="n">
+        <v>19.72752571105957</v>
+      </c>
+      <c r="C5" t="n">
+        <v>34.34500122070312</v>
+      </c>
+      <c r="D5" t="n">
+        <v>146910400</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>38868</v>
+      </c>
+      <c r="B6" t="n">
+        <v>19.20835304260254</v>
+      </c>
+      <c r="C6" t="n">
+        <v>33.18500137329102</v>
+      </c>
+      <c r="D6" t="n">
+        <v>199376800</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>38898</v>
+      </c>
+      <c r="B7" t="n">
+        <v>19.41383934020996</v>
+      </c>
+      <c r="C7" t="n">
+        <v>33.54000091552734</v>
+      </c>
+      <c r="D7" t="n">
+        <v>231396200</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>38929</v>
+      </c>
+      <c r="B8" t="n">
+        <v>20.93614959716797</v>
+      </c>
+      <c r="C8" t="n">
+        <v>36.16999816894531</v>
+      </c>
+      <c r="D8" t="n">
+        <v>210154800</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>38960</v>
+      </c>
+      <c r="B9" t="n">
+        <v>20.27071189880371</v>
+      </c>
+      <c r="C9" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>187720300</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>38990</v>
+      </c>
+      <c r="B10" t="n">
+        <v>21.1048698425293</v>
+      </c>
+      <c r="C10" t="n">
+        <v>36.18000030517578</v>
+      </c>
+      <c r="D10" t="n">
+        <v>132945900</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>39021</v>
+      </c>
+      <c r="B11" t="n">
+        <v>21.16903114318848</v>
+      </c>
+      <c r="C11" t="n">
+        <v>36.29000091552734</v>
+      </c>
+      <c r="D11" t="n">
+        <v>143373800</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>39051</v>
+      </c>
+      <c r="B12" t="n">
+        <v>20.71637916564941</v>
+      </c>
+      <c r="C12" t="n">
+        <v>35.2400016784668</v>
+      </c>
+      <c r="D12" t="n">
+        <v>152557700</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>39082</v>
+      </c>
+      <c r="B13" t="n">
+        <v>20.90449714660645</v>
+      </c>
+      <c r="C13" t="n">
+        <v>35.56000137329102</v>
+      </c>
+      <c r="D13" t="n">
+        <v>168467400</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>39113</v>
+      </c>
+      <c r="B14" t="n">
+        <v>21.28211402893066</v>
+      </c>
+      <c r="C14" t="n">
+        <v>35.91999816894531</v>
+      </c>
+      <c r="D14" t="n">
+        <v>211952100</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>39141</v>
+      </c>
+      <c r="B15" t="n">
+        <v>20.55928039550781</v>
+      </c>
+      <c r="C15" t="n">
+        <v>34.70000076293945</v>
+      </c>
+      <c r="D15" t="n">
+        <v>212814000</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>39172</v>
+      </c>
+      <c r="B16" t="n">
+        <v>20.39932441711426</v>
+      </c>
+      <c r="C16" t="n">
+        <v>34.43000030517578</v>
+      </c>
+      <c r="D16" t="n">
+        <v>321594000</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>39202</v>
+      </c>
+      <c r="B17" t="n">
+        <v>21.26433753967285</v>
+      </c>
+      <c r="C17" t="n">
+        <v>35.88999938964844</v>
+      </c>
+      <c r="D17" t="n">
+        <v>272744000</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>39233</v>
+      </c>
+      <c r="B18" t="n">
+        <v>21.55026245117188</v>
+      </c>
+      <c r="C18" t="n">
+        <v>36.09000015258789</v>
+      </c>
+      <c r="D18" t="n">
+        <v>240678600</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>39263</v>
+      </c>
+      <c r="B19" t="n">
+        <v>21.00089836120605</v>
+      </c>
+      <c r="C19" t="n">
+        <v>35.16999816894531</v>
+      </c>
+      <c r="D19" t="n">
+        <v>238282500</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>39294</v>
+      </c>
+      <c r="B20" t="n">
+        <v>20.16493606567383</v>
+      </c>
+      <c r="C20" t="n">
+        <v>33.77000045776367</v>
+      </c>
+      <c r="D20" t="n">
+        <v>347010100</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>39325</v>
+      </c>
+      <c r="B21" t="n">
+        <v>22.01457214355469</v>
+      </c>
+      <c r="C21" t="n">
+        <v>36.54000091552734</v>
+      </c>
+      <c r="D21" t="n">
+        <v>574757900</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>39355</v>
+      </c>
+      <c r="B22" t="n">
+        <v>21.46029281616211</v>
+      </c>
+      <c r="C22" t="n">
+        <v>35.61999893188477</v>
+      </c>
+      <c r="D22" t="n">
+        <v>299603100</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>39386</v>
+      </c>
+      <c r="B23" t="n">
+        <v>20.49029350280762</v>
+      </c>
+      <c r="C23" t="n">
+        <v>34.0099983215332</v>
+      </c>
+      <c r="D23" t="n">
+        <v>436520200</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>39416</v>
+      </c>
+      <c r="B24" t="n">
+        <v>19.72395324707031</v>
+      </c>
+      <c r="C24" t="n">
+        <v>32.43000030517578</v>
+      </c>
+      <c r="D24" t="n">
+        <v>725189100</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>39447</v>
+      </c>
+      <c r="B25" t="n">
+        <v>18.36157989501953</v>
+      </c>
+      <c r="C25" t="n">
+        <v>30.19000053405762</v>
+      </c>
+      <c r="D25" t="n">
+        <v>438998200</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>39478</v>
+      </c>
+      <c r="B26" t="n">
+        <v>20.72749328613281</v>
+      </c>
+      <c r="C26" t="n">
+        <v>34.08000183105469</v>
+      </c>
+      <c r="D26" t="n">
+        <v>946469700</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>39507</v>
+      </c>
+      <c r="B27" t="n">
+        <v>17.96043395996094</v>
+      </c>
+      <c r="C27" t="n">
+        <v>29.22999954223633</v>
+      </c>
+      <c r="D27" t="n">
+        <v>633972700</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>39538</v>
+      </c>
+      <c r="B28" t="n">
+        <v>17.88056182861328</v>
+      </c>
+      <c r="C28" t="n">
+        <v>29.10000038146973</v>
+      </c>
+      <c r="D28" t="n">
+        <v>803046600</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>39568</v>
+      </c>
+      <c r="B29" t="n">
+        <v>18.27995300292969</v>
+      </c>
+      <c r="C29" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="D29" t="n">
+        <v>682338000</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>39599</v>
+      </c>
+      <c r="B30" t="n">
+        <v>17.11006546020508</v>
+      </c>
+      <c r="C30" t="n">
+        <v>27.56999969482422</v>
+      </c>
+      <c r="D30" t="n">
+        <v>547243800</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>39629</v>
+      </c>
+      <c r="B31" t="n">
+        <v>14.73936462402344</v>
+      </c>
+      <c r="C31" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="D31" t="n">
+        <v>881900200</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>39660</v>
+      </c>
+      <c r="B32" t="n">
+        <v>18.78570365905762</v>
+      </c>
+      <c r="C32" t="n">
+        <v>30.27000045776367</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1650558200</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>39691</v>
+      </c>
+      <c r="B33" t="n">
+        <v>18.99042129516602</v>
+      </c>
+      <c r="C33" t="n">
+        <v>30.27000045776367</v>
+      </c>
+      <c r="D33" t="n">
+        <v>900294300</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>39721</v>
+      </c>
+      <c r="B34" t="n">
+        <v>23.54510116577148</v>
+      </c>
+      <c r="C34" t="n">
+        <v>37.52999877929688</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1440024400</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>39752</v>
+      </c>
+      <c r="B35" t="n">
+        <v>21.36186981201172</v>
+      </c>
+      <c r="C35" t="n">
+        <v>34.04999923706055</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1562646700</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>39782</v>
+      </c>
+      <c r="B36" t="n">
+        <v>18.30188369750977</v>
+      </c>
+      <c r="C36" t="n">
+        <v>28.88999938964844</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1659766400</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>39813</v>
+      </c>
+      <c r="B37" t="n">
+        <v>18.67565155029297</v>
+      </c>
+      <c r="C37" t="n">
+        <v>29.47999954223633</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1161129200</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>39844</v>
+      </c>
+      <c r="B38" t="n">
+        <v>11.9731969833374</v>
+      </c>
+      <c r="C38" t="n">
+        <v>18.89999961853027</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1982060300</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>39872</v>
+      </c>
+      <c r="B39" t="n">
+        <v>7.808657169342041</v>
+      </c>
+      <c r="C39" t="n">
+        <v>12.10000038146973</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2904697900</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39903</v>
+      </c>
+      <c r="B40" t="n">
+        <v>9.189694404602051</v>
+      </c>
+      <c r="C40" t="n">
+        <v>14.23999977111816</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4175955300</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>39933</v>
+      </c>
+      <c r="B41" t="n">
+        <v>12.91332244873047</v>
+      </c>
+      <c r="C41" t="n">
+        <v>20.01000022888184</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3466752800</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>39964</v>
+      </c>
+      <c r="B42" t="n">
+        <v>16.49169731140137</v>
+      </c>
+      <c r="C42" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3207485400</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>39994</v>
+      </c>
+      <c r="B43" t="n">
+        <v>15.68974113464355</v>
+      </c>
+      <c r="C43" t="n">
+        <v>24.26000022888184</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1694313800</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>40025</v>
+      </c>
+      <c r="B44" t="n">
+        <v>15.81909084320068</v>
+      </c>
+      <c r="C44" t="n">
+        <v>24.45999908447266</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1571347200</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>40056</v>
+      </c>
+      <c r="B45" t="n">
+        <v>17.83167457580566</v>
+      </c>
+      <c r="C45" t="n">
+        <v>27.52000045776367</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1135839100</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>4671609008</v>
+      </c>
+      <c r="H45" t="n">
+        <v>128562682038.6529</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.2431365934210049</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>40086</v>
+      </c>
+      <c r="B46" t="n">
+        <v>18.25933074951172</v>
+      </c>
+      <c r="C46" t="n">
+        <v>28.18000030517578</v>
+      </c>
+      <c r="D46" t="n">
+        <v>877493500</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>4671609008</v>
+      </c>
+      <c r="H46" t="n">
+        <v>131645943271.1019</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.1878353900117319</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>40117</v>
+      </c>
+      <c r="B47" t="n">
+        <v>17.83167457580566</v>
+      </c>
+      <c r="C47" t="n">
+        <v>27.52000045776367</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1179369400</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>4671609008</v>
+      </c>
+      <c r="H47" t="n">
+        <v>128562682038.6529</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.2524546463499756</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>40147</v>
+      </c>
+      <c r="B48" t="n">
+        <v>18.2014217376709</v>
+      </c>
+      <c r="C48" t="n">
+        <v>28.04000091552734</v>
+      </c>
+      <c r="D48" t="n">
+        <v>740587500</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>4685063588</v>
+      </c>
+      <c r="H48" t="n">
+        <v>131369187296.8238</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.1580741618741077</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>40178</v>
+      </c>
+      <c r="B49" t="n">
+        <v>17.51984596252441</v>
+      </c>
+      <c r="C49" t="n">
+        <v>26.98999977111816</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1251545400</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>4685063588</v>
+      </c>
+      <c r="H49" t="n">
+        <v>126449865167.794</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.2671352003002953</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>40209</v>
+      </c>
+      <c r="B50" t="n">
+        <v>18.45458221435547</v>
+      </c>
+      <c r="C50" t="n">
+        <v>28.43000030517578</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1009905300</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>4685063588</v>
+      </c>
+      <c r="H50" t="n">
+        <v>133196359236.6079</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.2155585043897167</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>40237</v>
+      </c>
+      <c r="B51" t="n">
+        <v>17.77791595458984</v>
+      </c>
+      <c r="C51" t="n">
+        <v>27.34000015258789</v>
+      </c>
+      <c r="D51" t="n">
+        <v>840453900</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>4237777218</v>
+      </c>
+      <c r="H51" t="n">
+        <v>115860829786.7535</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.1983242291336514</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>40268</v>
+      </c>
+      <c r="B52" t="n">
+        <v>20.23586845397949</v>
+      </c>
+      <c r="C52" t="n">
+        <v>31.1200008392334</v>
+      </c>
+      <c r="D52" t="n">
+        <v>817434600</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>4237777218</v>
+      </c>
+      <c r="H52" t="n">
+        <v>131879630580.6442</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.1928923013054907</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>40298</v>
+      </c>
+      <c r="B53" t="n">
+        <v>21.52987480163574</v>
+      </c>
+      <c r="C53" t="n">
+        <v>33.11000061035156</v>
+      </c>
+      <c r="D53" t="n">
+        <v>943549600</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>4237777218</v>
+      </c>
+      <c r="H53" t="n">
+        <v>140312806274.5139</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.2226520063377244</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>40329</v>
+      </c>
+      <c r="B54" t="n">
+        <v>18.68411445617676</v>
+      </c>
+      <c r="C54" t="n">
+        <v>28.69000053405762</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1142687200</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>5210152080</v>
+      </c>
+      <c r="H54" t="n">
+        <v>149479265957.7214</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.219319356221172</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>40359</v>
+      </c>
+      <c r="B55" t="n">
+        <v>16.67177581787109</v>
+      </c>
+      <c r="C55" t="n">
+        <v>25.60000038146973</v>
+      </c>
+      <c r="D55" t="n">
+        <v>916736600</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>5210152080</v>
+      </c>
+      <c r="H55" t="n">
+        <v>133379895235.5153</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.1759519848794893</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>40390</v>
+      </c>
+      <c r="B56" t="n">
+        <v>18.05891990661621</v>
+      </c>
+      <c r="C56" t="n">
+        <v>27.72999954223633</v>
+      </c>
+      <c r="D56" t="n">
+        <v>800299500</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>5210152080</v>
+      </c>
+      <c r="H56" t="n">
+        <v>144477514793.3817</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.153603865628429</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>40421</v>
+      </c>
+      <c r="B57" t="n">
+        <v>15.36405658721924</v>
+      </c>
+      <c r="C57" t="n">
+        <v>23.54999923706055</v>
+      </c>
+      <c r="D57" t="n">
+        <v>811768100</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>5233424661</v>
+      </c>
+      <c r="H57" t="n">
+        <v>123247146773.7639</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.1551122166808622</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>40451</v>
+      </c>
+      <c r="B58" t="n">
+        <v>16.3883228302002</v>
+      </c>
+      <c r="C58" t="n">
+        <v>25.1200008392334</v>
+      </c>
+      <c r="D58" t="n">
+        <v>745446900</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>5233424661</v>
+      </c>
+      <c r="H58" t="n">
+        <v>131463631876.3848</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.1424395970682724</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>40482</v>
+      </c>
+      <c r="B59" t="n">
+        <v>17.0015811920166</v>
+      </c>
+      <c r="C59" t="n">
+        <v>26.05999946594238</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1025608100</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>5233424661</v>
+      </c>
+      <c r="H59" t="n">
+        <v>136383043870.7097</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.1959726501162677</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>40512</v>
+      </c>
+      <c r="B60" t="n">
+        <v>17.78607940673828</v>
+      </c>
+      <c r="C60" t="n">
+        <v>27.20999908447266</v>
+      </c>
+      <c r="D60" t="n">
+        <v>686309700</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>5244376763</v>
+      </c>
+      <c r="H60" t="n">
+        <v>142699486919.8597</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.1308658265824903</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>40543</v>
+      </c>
+      <c r="B61" t="n">
+        <v>20.25691986083984</v>
+      </c>
+      <c r="C61" t="n">
+        <v>30.98999977111816</v>
+      </c>
+      <c r="D61" t="n">
+        <v>614774500</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>5244376763</v>
+      </c>
+      <c r="H61" t="n">
+        <v>162523234685.0274</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.1172254641080218</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>40574</v>
+      </c>
+      <c r="B62" t="n">
+        <v>21.191650390625</v>
+      </c>
+      <c r="C62" t="n">
+        <v>32.41999816894531</v>
+      </c>
+      <c r="D62" t="n">
+        <v>683995900</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>5244376763</v>
+      </c>
+      <c r="H62" t="n">
+        <v>170022685053.7194</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.1304246302107261</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>40602</v>
+      </c>
+      <c r="B63" t="n">
+        <v>21.11864280700684</v>
+      </c>
+      <c r="C63" t="n">
+        <v>32.2599983215332</v>
+      </c>
+      <c r="D63" t="n">
+        <v>707641800</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="F63" t="n">
+        <v>14.59728430838607</v>
+      </c>
+      <c r="G63" t="n">
+        <v>5268078757</v>
+      </c>
+      <c r="H63" t="n">
+        <v>169948211858.5247</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.1343263517197262</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>40633</v>
+      </c>
+      <c r="B64" t="n">
+        <v>20.80489540100098</v>
+      </c>
+      <c r="C64" t="n">
+        <v>31.70999908447266</v>
+      </c>
+      <c r="D64" t="n">
+        <v>711238900</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="F64" t="n">
+        <v>14.34841587532699</v>
+      </c>
+      <c r="G64" t="n">
+        <v>5268078757</v>
+      </c>
+      <c r="H64" t="n">
+        <v>167050772561.3998</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.1350091623165155</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>40663</v>
+      </c>
+      <c r="B65" t="n">
+        <v>19.09904670715332</v>
+      </c>
+      <c r="C65" t="n">
+        <v>29.11000061035156</v>
+      </c>
+      <c r="D65" t="n">
+        <v>828884300</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="F65" t="n">
+        <v>13.17194597753464</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5268078757</v>
+      </c>
+      <c r="H65" t="n">
+        <v>153353775831.6501</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.1573409089411607</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>40694</v>
+      </c>
+      <c r="B66" t="n">
+        <v>18.68952941894531</v>
+      </c>
+      <c r="C66" t="n">
+        <v>28.3700008392334</v>
+      </c>
+      <c r="D66" t="n">
+        <v>618422100</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="F66" t="n">
+        <v>11.6748974647051</v>
+      </c>
+      <c r="G66" t="n">
+        <v>5289099076</v>
+      </c>
+      <c r="H66" t="n">
+        <v>150051745224.9086</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.1169239016160944</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>40724</v>
+      </c>
+      <c r="B67" t="n">
+        <v>18.48530387878418</v>
+      </c>
+      <c r="C67" t="n">
+        <v>28.05999946594238</v>
+      </c>
+      <c r="D67" t="n">
+        <v>894779600</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="F67" t="n">
+        <v>11.54732488310386</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5289099076</v>
+      </c>
+      <c r="H67" t="n">
+        <v>148412117247.8763</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.1691742936070498</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>40755</v>
+      </c>
+      <c r="B68" t="n">
+        <v>18.40625381469727</v>
+      </c>
+      <c r="C68" t="n">
+        <v>27.94000053405762</v>
+      </c>
+      <c r="D68" t="n">
+        <v>674137600</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="F68" t="n">
+        <v>11.49794260660807</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5289099076</v>
+      </c>
+      <c r="H68" t="n">
+        <v>147777431008.1237</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.1274579262579879</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>40786</v>
+      </c>
+      <c r="B69" t="n">
+        <v>17.27035331726074</v>
+      </c>
+      <c r="C69" t="n">
+        <v>26.10000038146973</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1181099400</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F69" t="n">
+        <v>10.11627921762392</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5279840998</v>
+      </c>
+      <c r="H69" t="n">
+        <v>137803852061.8995</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.2236998046811257</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>40816</v>
+      </c>
+      <c r="B70" t="n">
+        <v>15.96018981933594</v>
+      </c>
+      <c r="C70" t="n">
+        <v>24.1200008392334</v>
+      </c>
+      <c r="D70" t="n">
+        <v>894820200</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F70" t="n">
+        <v>9.348837534586588</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5279840998</v>
+      </c>
+      <c r="H70" t="n">
+        <v>127349769302.7789</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.1694786264091963</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>40847</v>
+      </c>
+      <c r="B71" t="n">
+        <v>17.14463043212891</v>
+      </c>
+      <c r="C71" t="n">
+        <v>25.90999984741211</v>
+      </c>
+      <c r="D71" t="n">
+        <v>988797700</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F71" t="n">
+        <v>10.04263559977213</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5279840998</v>
+      </c>
+      <c r="H71" t="n">
+        <v>136800679452.5402</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.1872779313571291</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>40877</v>
+      </c>
+      <c r="B72" t="n">
+        <v>17.19484710693359</v>
+      </c>
+      <c r="C72" t="n">
+        <v>25.86000061035156</v>
+      </c>
+      <c r="D72" t="n">
+        <v>717310700</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F72" t="n">
+        <v>9.577778003833913</v>
+      </c>
+      <c r="G72" t="n">
+        <v>5273525555</v>
+      </c>
+      <c r="H72" t="n">
+        <v>136373374071.0046</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.1360210911123574</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>40908</v>
+      </c>
+      <c r="B73" t="n">
+        <v>18.32521438598633</v>
+      </c>
+      <c r="C73" t="n">
+        <v>27.55999946594238</v>
+      </c>
+      <c r="D73" t="n">
+        <v>600958300</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F73" t="n">
+        <v>10.20740720960829</v>
+      </c>
+      <c r="G73" t="n">
+        <v>5273525555</v>
+      </c>
+      <c r="H73" t="n">
+        <v>145338361479.4335</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.1139575970064679</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>40939</v>
+      </c>
+      <c r="B74" t="n">
+        <v>19.42232704162598</v>
+      </c>
+      <c r="C74" t="n">
+        <v>29.20999908447266</v>
+      </c>
+      <c r="D74" t="n">
+        <v>707418200</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F74" t="n">
+        <v>10.81851817943432</v>
+      </c>
+      <c r="G74" t="n">
+        <v>5273525555</v>
+      </c>
+      <c r="H74" t="n">
+        <v>154039676633.4932</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.1341452113243813</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>40968</v>
+      </c>
+      <c r="B75" t="n">
+        <v>20.89118576049805</v>
+      </c>
+      <c r="C75" t="n">
+        <v>31.29000091552734</v>
+      </c>
+      <c r="D75" t="n">
+        <v>574647800</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.09574500550615</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5273240691</v>
+      </c>
+      <c r="H75" t="n">
+        <v>164999706049.186</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.1089743164920897</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>40999</v>
+      </c>
+      <c r="B76" t="n">
+        <v>22.86123085021973</v>
+      </c>
+      <c r="C76" t="n">
+        <v>34.13999938964844</v>
+      </c>
+      <c r="D76" t="n">
+        <v>697532800</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F76" t="n">
+        <v>12.10638276228668</v>
+      </c>
+      <c r="G76" t="n">
+        <v>5273240691</v>
+      </c>
+      <c r="H76" t="n">
+        <v>180028433972.2093</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.1322778232350555</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>41029</v>
+      </c>
+      <c r="B77" t="n">
+        <v>22.37909317016602</v>
+      </c>
+      <c r="C77" t="n">
+        <v>33.41999816894531</v>
+      </c>
+      <c r="D77" t="n">
+        <v>511250200</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F77" t="n">
+        <v>11.85106318047706</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5273240691</v>
+      </c>
+      <c r="H77" t="n">
+        <v>176231694237.6279</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09695180439469911</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>41060</v>
+      </c>
+      <c r="B78" t="n">
+        <v>21.60109710693359</v>
+      </c>
+      <c r="C78" t="n">
+        <v>32.04999923706055</v>
+      </c>
+      <c r="D78" t="n">
+        <v>636432600</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F78" t="n">
+        <v>11.05172387484846</v>
+      </c>
+      <c r="G78" t="n">
+        <v>5313919450</v>
+      </c>
+      <c r="H78" t="n">
+        <v>170311114318.3012</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.1197670770113009</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>41090</v>
+      </c>
+      <c r="B79" t="n">
+        <v>22.53793525695801</v>
+      </c>
+      <c r="C79" t="n">
+        <v>33.43999862670898</v>
+      </c>
+      <c r="D79" t="n">
+        <v>638521500</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F79" t="n">
+        <v>11.53103400920999</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5313919450</v>
+      </c>
+      <c r="H79" t="n">
+        <v>177697459110.4422</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.1201601766846503</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>41121</v>
+      </c>
+      <c r="B80" t="n">
+        <v>22.78730392456055</v>
+      </c>
+      <c r="C80" t="n">
+        <v>33.81000137329102</v>
+      </c>
+      <c r="D80" t="n">
+        <v>494208900</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F80" t="n">
+        <v>11.6586211632038</v>
+      </c>
+      <c r="G80" t="n">
+        <v>5313919450</v>
+      </c>
+      <c r="H80" t="n">
+        <v>179663623902.0578</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09300270819874773</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>41152</v>
+      </c>
+      <c r="B81" t="n">
+        <v>23.08513259887695</v>
+      </c>
+      <c r="C81" t="n">
+        <v>34.02999877929688</v>
+      </c>
+      <c r="D81" t="n">
+        <v>414112100</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F81" t="n">
+        <v>11.26821151632347</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5282185586</v>
+      </c>
+      <c r="H81" t="n">
+        <v>179752769043.5995</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.07839787021068896</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>41182</v>
+      </c>
+      <c r="B82" t="n">
+        <v>23.42431640625</v>
+      </c>
+      <c r="C82" t="n">
+        <v>34.52999877929688</v>
+      </c>
+      <c r="D82" t="n">
+        <v>528817300</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F82" t="n">
+        <v>11.43377443023075</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5282185586</v>
+      </c>
+      <c r="H82" t="n">
+        <v>182393861836.5995</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.1001133510722506</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>41213</v>
+      </c>
+      <c r="B83" t="n">
+        <v>22.8544864654541</v>
+      </c>
+      <c r="C83" t="n">
+        <v>33.68999862670898</v>
+      </c>
+      <c r="D83" t="n">
+        <v>605743100</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F83" t="n">
+        <v>11.15562868434072</v>
+      </c>
+      <c r="G83" t="n">
+        <v>5282185586</v>
+      </c>
+      <c r="H83" t="n">
+        <v>177956825138.362</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.1146766031101733</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>41243</v>
+      </c>
+      <c r="B84" t="n">
+        <v>22.53766059875488</v>
+      </c>
+      <c r="C84" t="n">
+        <v>33.0099983215332</v>
+      </c>
+      <c r="D84" t="n">
+        <v>444703800</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F84" t="n">
+        <v>10.38050261683434</v>
+      </c>
+      <c r="G84" t="n">
+        <v>5264273367</v>
+      </c>
+      <c r="H84" t="n">
+        <v>173773655008.7619</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.08447581821789538</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>41274</v>
+      </c>
+      <c r="B85" t="n">
+        <v>23.33647918701172</v>
+      </c>
+      <c r="C85" t="n">
+        <v>34.18000030517578</v>
+      </c>
+      <c r="D85" t="n">
+        <v>465866000</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F85" t="n">
+        <v>10.7484277689232</v>
+      </c>
+      <c r="G85" t="n">
+        <v>5264273367</v>
+      </c>
+      <c r="H85" t="n">
+        <v>179932865290.5887</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.08849578422738472</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>41305</v>
+      </c>
+      <c r="B86" t="n">
+        <v>23.95003318786621</v>
+      </c>
+      <c r="C86" t="n">
+        <v>34.83000183105469</v>
+      </c>
+      <c r="D86" t="n">
+        <v>524971600</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F86" t="n">
+        <v>10.95283076448261</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5264273367</v>
+      </c>
+      <c r="H86" t="n">
+        <v>183354651011.7824</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.09972346863498284</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>41333</v>
+      </c>
+      <c r="B87" t="n">
+        <v>24.1219367980957</v>
+      </c>
+      <c r="C87" t="n">
+        <v>35.08000183105469</v>
+      </c>
+      <c r="D87" t="n">
+        <v>461294400</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="F87" t="n">
+        <v>10.44047673543294</v>
+      </c>
+      <c r="G87" t="n">
+        <v>5270881531</v>
+      </c>
+      <c r="H87" t="n">
+        <v>184902533758.7523</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.08751750485890403</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>41364</v>
+      </c>
+      <c r="B88" t="n">
+        <v>25.43530654907227</v>
+      </c>
+      <c r="C88" t="n">
+        <v>36.9900016784668</v>
+      </c>
+      <c r="D88" t="n">
+        <v>443204500</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="F88" t="n">
+        <v>11.00892907097226</v>
+      </c>
+      <c r="G88" t="n">
+        <v>5270881531</v>
+      </c>
+      <c r="H88" t="n">
+        <v>194969916678.6896</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.08408546035295059</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>41394</v>
+      </c>
+      <c r="B89" t="n">
+        <v>26.11605262756348</v>
+      </c>
+      <c r="C89" t="n">
+        <v>37.97999954223633</v>
+      </c>
+      <c r="D89" t="n">
+        <v>468022100</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="F89" t="n">
+        <v>11.30357129233224</v>
+      </c>
+      <c r="G89" t="n">
+        <v>5270881531</v>
+      </c>
+      <c r="H89" t="n">
+        <v>200188078134.5619</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.08879389476833985</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>41425</v>
+      </c>
+      <c r="B90" t="n">
+        <v>28.10280609130859</v>
+      </c>
+      <c r="C90" t="n">
+        <v>40.54999923706055</v>
+      </c>
+      <c r="D90" t="n">
+        <v>461672500</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="F90" t="n">
+        <v>11.48725190851573</v>
+      </c>
+      <c r="G90" t="n">
+        <v>5296386944</v>
+      </c>
+      <c r="H90" t="n">
+        <v>214768486538.3774</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.08716744166945821</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>41455</v>
+      </c>
+      <c r="B91" t="n">
+        <v>28.60180282592773</v>
+      </c>
+      <c r="C91" t="n">
+        <v>41.27000045776367</v>
+      </c>
+      <c r="D91" t="n">
+        <v>433603700</v>
+      </c>
+      <c r="E91" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="F91" t="n">
+        <v>11.69121825998971</v>
+      </c>
+      <c r="G91" t="n">
+        <v>5296386944</v>
+      </c>
+      <c r="H91" t="n">
+        <v>218581891603.3735</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.08186782887742124</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>41486</v>
+      </c>
+      <c r="B92" t="n">
+        <v>30.14727020263672</v>
+      </c>
+      <c r="C92" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="D92" t="n">
+        <v>457853600</v>
+      </c>
+      <c r="E92" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="F92" t="n">
+        <v>12.32294617563739</v>
+      </c>
+      <c r="G92" t="n">
+        <v>5296386944</v>
+      </c>
+      <c r="H92" t="n">
+        <v>230392832064</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.08644640296130146</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>41517</v>
+      </c>
+      <c r="B93" t="n">
+        <v>28.66543769836426</v>
+      </c>
+      <c r="C93" t="n">
+        <v>41.08000183105469</v>
+      </c>
+      <c r="D93" t="n">
+        <v>321439400</v>
+      </c>
+      <c r="E93" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F93" t="n">
+        <v>11.13279182413406</v>
+      </c>
+      <c r="G93" t="n">
+        <v>5309782331</v>
+      </c>
+      <c r="H93" t="n">
+        <v>218125867879.9818</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.06053720848844341</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>41547</v>
+      </c>
+      <c r="B94" t="n">
+        <v>28.83290672302246</v>
+      </c>
+      <c r="C94" t="n">
+        <v>41.31999969482422</v>
+      </c>
+      <c r="D94" t="n">
+        <v>366625700</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F94" t="n">
+        <v>11.19783189561632</v>
+      </c>
+      <c r="G94" t="n">
+        <v>5309782331</v>
+      </c>
+      <c r="H94" t="n">
+        <v>219400204296.503</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.06904721835008872</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>41578</v>
+      </c>
+      <c r="B95" t="n">
+        <v>29.78888702392578</v>
+      </c>
+      <c r="C95" t="n">
+        <v>42.68999862670898</v>
+      </c>
+      <c r="D95" t="n">
+        <v>426027500</v>
+      </c>
+      <c r="E95" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F95" t="n">
+        <v>11.56910531889132</v>
+      </c>
+      <c r="G95" t="n">
+        <v>5309782331</v>
+      </c>
+      <c r="H95" t="n">
+        <v>226674600418.5136</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.08023445660149416</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>41608</v>
+      </c>
+      <c r="B96" t="n">
+        <v>30.93464660644531</v>
+      </c>
+      <c r="C96" t="n">
+        <v>44.02000045776367</v>
+      </c>
+      <c r="D96" t="n">
+        <v>315449500</v>
+      </c>
+      <c r="E96" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F96" t="n">
+        <v>11.58421064677991</v>
+      </c>
+      <c r="G96" t="n">
+        <v>5267598642</v>
+      </c>
+      <c r="H96" t="n">
+        <v>231879694632.1553</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.05988487761478924</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>41639</v>
+      </c>
+      <c r="B97" t="n">
+        <v>31.90442657470703</v>
+      </c>
+      <c r="C97" t="n">
+        <v>45.40000152587891</v>
+      </c>
+      <c r="D97" t="n">
+        <v>325412900</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F97" t="n">
+        <v>11.94736882259971</v>
+      </c>
+      <c r="G97" t="n">
+        <v>5267598642</v>
+      </c>
+      <c r="H97" t="n">
+        <v>239148986384.5176</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.0617763277189333</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>41670</v>
+      </c>
+      <c r="B98" t="n">
+        <v>31.86226654052734</v>
+      </c>
+      <c r="C98" t="n">
+        <v>45.34000015258789</v>
+      </c>
+      <c r="D98" t="n">
+        <v>387760100</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F98" t="n">
+        <v>11.93157898752313</v>
+      </c>
+      <c r="G98" t="n">
+        <v>5267598642</v>
+      </c>
+      <c r="H98" t="n">
+        <v>238832923232.0518</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.07361230920447943</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>41698</v>
+      </c>
+      <c r="B99" t="n">
+        <v>32.84130096435547</v>
+      </c>
+      <c r="C99" t="n">
+        <v>46.41999816894531</v>
+      </c>
+      <c r="D99" t="n">
+        <v>303124800</v>
+      </c>
+      <c r="E99" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F99" t="n">
+        <v>11.93316148301936</v>
+      </c>
+      <c r="G99" t="n">
+        <v>5261842959</v>
+      </c>
+      <c r="H99" t="n">
+        <v>244254740522.0578</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.05760810468155973</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>41729</v>
+      </c>
+      <c r="B100" t="n">
+        <v>35.19012451171875</v>
+      </c>
+      <c r="C100" t="n">
+        <v>49.7400016784668</v>
+      </c>
+      <c r="D100" t="n">
+        <v>367718800</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F100" t="n">
+        <v>12.78663282222797</v>
+      </c>
+      <c r="G100" t="n">
+        <v>5261842959</v>
+      </c>
+      <c r="H100" t="n">
+        <v>261724077612.4887</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.06988403167202922</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>41759</v>
+      </c>
+      <c r="B101" t="n">
+        <v>35.1193962097168</v>
+      </c>
+      <c r="C101" t="n">
+        <v>49.63999938964844</v>
+      </c>
+      <c r="D101" t="n">
+        <v>374101800</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="F101" t="n">
+        <v>12.76092529296875</v>
+      </c>
+      <c r="G101" t="n">
+        <v>5261842959</v>
+      </c>
+      <c r="H101" t="n">
+        <v>261197881273.1859</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.07109710474352451</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>41790</v>
+      </c>
+      <c r="B102" t="n">
+        <v>36.18390274047852</v>
+      </c>
+      <c r="C102" t="n">
+        <v>50.77999877929688</v>
+      </c>
+      <c r="D102" t="n">
+        <v>283041300</v>
+      </c>
+      <c r="E102" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F102" t="n">
+        <v>12.63184049236241</v>
+      </c>
+      <c r="G102" t="n">
+        <v>5267069638</v>
+      </c>
+      <c r="H102" t="n">
+        <v>267461789788.1116</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.05373790730959005</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>41820</v>
+      </c>
+      <c r="B103" t="n">
+        <v>37.45226669311523</v>
+      </c>
+      <c r="C103" t="n">
+        <v>52.56000137329102</v>
+      </c>
+      <c r="D103" t="n">
+        <v>291434500</v>
+      </c>
+      <c r="E103" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F103" t="n">
+        <v>13.07462720728632</v>
+      </c>
+      <c r="G103" t="n">
+        <v>5267069638</v>
+      </c>
+      <c r="H103" t="n">
+        <v>276837187406.4994</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.0553314309530684</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>41851</v>
+      </c>
+      <c r="B104" t="n">
+        <v>36.26940536499023</v>
+      </c>
+      <c r="C104" t="n">
+        <v>50.90000152587891</v>
+      </c>
+      <c r="D104" t="n">
+        <v>350004200</v>
+      </c>
+      <c r="E104" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="F104" t="n">
+        <v>12.66169192186042</v>
+      </c>
+      <c r="G104" t="n">
+        <v>5267069638</v>
+      </c>
+      <c r="H104" t="n">
+        <v>268093852611.1105</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.0664514092380413</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>41882</v>
+      </c>
+      <c r="B105" t="n">
+        <v>36.91051864624023</v>
+      </c>
+      <c r="C105" t="n">
+        <v>51.43999862670898</v>
+      </c>
+      <c r="D105" t="n">
+        <v>243207400</v>
+      </c>
+      <c r="E105" t="n">
+        <v>4.050000000000001</v>
+      </c>
+      <c r="F105" t="n">
+        <v>12.70123422881703</v>
+      </c>
+      <c r="G105" t="n">
+        <v>5220407047</v>
+      </c>
+      <c r="H105" t="n">
+        <v>268537731328.5419</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.0465878230970061</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>41912</v>
+      </c>
+      <c r="B106" t="n">
+        <v>37.21904754638672</v>
+      </c>
+      <c r="C106" t="n">
+        <v>51.86999893188477</v>
+      </c>
+      <c r="D106" t="n">
+        <v>272704900</v>
+      </c>
+      <c r="E106" t="n">
+        <v>4.050000000000001</v>
+      </c>
+      <c r="F106" t="n">
+        <v>12.80740714367525</v>
+      </c>
+      <c r="G106" t="n">
+        <v>5220407047</v>
+      </c>
+      <c r="H106" t="n">
+        <v>270782507951.8937</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.05223824455541541</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>41943</v>
+      </c>
+      <c r="B107" t="n">
+        <v>38.09445953369141</v>
+      </c>
+      <c r="C107" t="n">
+        <v>53.09000015258789</v>
+      </c>
+      <c r="D107" t="n">
+        <v>438607500</v>
+      </c>
+      <c r="E107" t="n">
+        <v>4.050000000000001</v>
+      </c>
+      <c r="F107" t="n">
+        <v>13.10864201298466</v>
+      </c>
+      <c r="G107" t="n">
+        <v>5220407047</v>
+      </c>
+      <c r="H107" t="n">
+        <v>277151410921.8009</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.08401787371198452</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>41973</v>
+      </c>
+      <c r="B108" t="n">
+        <v>39.35037612915039</v>
+      </c>
+      <c r="C108" t="n">
+        <v>54.47999954223633</v>
+      </c>
+      <c r="D108" t="n">
+        <v>238274700</v>
+      </c>
+      <c r="E108" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="F108" t="n">
+        <v>13.35294106427361</v>
+      </c>
+      <c r="G108" t="n">
+        <v>5187624483</v>
+      </c>
+      <c r="H108" t="n">
+        <v>282621779459.134</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.04593137008679662</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>42004</v>
+      </c>
+      <c r="B109" t="n">
+        <v>39.59596633911133</v>
+      </c>
+      <c r="C109" t="n">
+        <v>54.81999969482422</v>
+      </c>
+      <c r="D109" t="n">
+        <v>356501200</v>
+      </c>
+      <c r="E109" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="F109" t="n">
+        <v>13.43627443500594</v>
+      </c>
+      <c r="G109" t="n">
+        <v>5187624483</v>
+      </c>
+      <c r="H109" t="n">
+        <v>284385572574.9227</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.06872147380140275</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>42035</v>
+      </c>
+      <c r="B110" t="n">
+        <v>37.50132751464844</v>
+      </c>
+      <c r="C110" t="n">
+        <v>51.91999816894531</v>
+      </c>
+      <c r="D110" t="n">
+        <v>388756400</v>
+      </c>
+      <c r="E110" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="F110" t="n">
+        <v>12.72548974729052</v>
+      </c>
+      <c r="G110" t="n">
+        <v>5187624483</v>
+      </c>
+      <c r="H110" t="n">
+        <v>269341453658.5359</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.07493919447600078</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>42063</v>
+      </c>
+      <c r="B111" t="n">
+        <v>39.83514404296875</v>
+      </c>
+      <c r="C111" t="n">
+        <v>54.79000091552734</v>
+      </c>
+      <c r="D111" t="n">
+        <v>278034600</v>
+      </c>
+      <c r="E111" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F111" t="n">
+        <v>13.3634148574457</v>
+      </c>
+      <c r="G111" t="n">
+        <v>5152280886</v>
+      </c>
+      <c r="H111" t="n">
+        <v>282293474460.994</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.05396340109396745</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>42094</v>
+      </c>
+      <c r="B112" t="n">
+        <v>39.55159759521484</v>
+      </c>
+      <c r="C112" t="n">
+        <v>54.40000152587891</v>
+      </c>
+      <c r="D112" t="n">
+        <v>348820200</v>
+      </c>
+      <c r="E112" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F112" t="n">
+        <v>13.26829305509242</v>
+      </c>
+      <c r="G112" t="n">
+        <v>5152280886</v>
+      </c>
+      <c r="H112" t="n">
+        <v>280284088060.1567</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.06770209305704379</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>42124</v>
+      </c>
+      <c r="B113" t="n">
+        <v>40.06052780151367</v>
+      </c>
+      <c r="C113" t="n">
+        <v>55.09999847412109</v>
+      </c>
+      <c r="D113" t="n">
+        <v>309923300</v>
+      </c>
+      <c r="E113" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F113" t="n">
+        <v>13.43902401807832</v>
+      </c>
+      <c r="G113" t="n">
+        <v>5152280886</v>
+      </c>
+      <c r="H113" t="n">
+        <v>283890668956.8433</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.0601526405212373</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>42155</v>
+      </c>
+      <c r="B114" t="n">
+        <v>40.96147155761719</v>
+      </c>
+      <c r="C114" t="n">
+        <v>55.95999908447266</v>
+      </c>
+      <c r="D114" t="n">
+        <v>266599600</v>
+      </c>
+      <c r="E114" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="F114" t="n">
+        <v>13.68215136539674</v>
+      </c>
+      <c r="G114" t="n">
+        <v>5149204973</v>
+      </c>
+      <c r="H114" t="n">
+        <v>288149505574.842</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.05177490532964262</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>42185</v>
+      </c>
+      <c r="B115" t="n">
+        <v>41.16641998291016</v>
+      </c>
+      <c r="C115" t="n">
+        <v>56.2400016784668</v>
+      </c>
+      <c r="D115" t="n">
+        <v>362266300</v>
+      </c>
+      <c r="E115" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="F115" t="n">
+        <v>13.75061165732685</v>
+      </c>
+      <c r="G115" t="n">
+        <v>5149204973</v>
+      </c>
+      <c r="H115" t="n">
+        <v>289591296324.2896</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.07035383168849434</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>42216</v>
+      </c>
+      <c r="B116" t="n">
+        <v>42.35953903198242</v>
+      </c>
+      <c r="C116" t="n">
+        <v>57.86999893188477</v>
+      </c>
+      <c r="D116" t="n">
+        <v>300870000</v>
+      </c>
+      <c r="E116" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="F116" t="n">
+        <v>14.14914399312586</v>
+      </c>
+      <c r="G116" t="n">
+        <v>5149204973</v>
+      </c>
+      <c r="H116" t="n">
+        <v>297984486287.5657</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.05843037936489618</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>42247</v>
+      </c>
+      <c r="B117" t="n">
+        <v>39.29121398925781</v>
+      </c>
+      <c r="C117" t="n">
+        <v>53.33000183105469</v>
+      </c>
+      <c r="D117" t="n">
+        <v>383406500</v>
+      </c>
+      <c r="E117" t="n">
+        <v>4.109999999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>12.97566954526878</v>
+      </c>
+      <c r="G117" t="n">
+        <v>5133359268</v>
+      </c>
+      <c r="H117" t="n">
+        <v>273762059161.9016</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.07468920057671677</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>42277</v>
+      </c>
+      <c r="B118" t="n">
+        <v>37.83243179321289</v>
+      </c>
+      <c r="C118" t="n">
+        <v>51.34999847412109</v>
+      </c>
+      <c r="D118" t="n">
+        <v>409157600</v>
+      </c>
+      <c r="E118" t="n">
+        <v>4.109999999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>12.4939169036791</v>
+      </c>
+      <c r="G118" t="n">
+        <v>5133359268</v>
+      </c>
+      <c r="H118" t="n">
+        <v>263597990578.9154</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.07970562328465493</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>42308</v>
+      </c>
+      <c r="B119" t="n">
+        <v>39.88798141479492</v>
+      </c>
+      <c r="C119" t="n">
+        <v>54.13999938964844</v>
+      </c>
+      <c r="D119" t="n">
+        <v>353524000</v>
+      </c>
+      <c r="E119" t="n">
+        <v>4.109999999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>13.17274924322347</v>
+      </c>
+      <c r="G119" t="n">
+        <v>5133359268</v>
+      </c>
+      <c r="H119" t="n">
+        <v>277920067636.3661</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.06886796375304859</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>42338</v>
+      </c>
+      <c r="B120" t="n">
+        <v>40.87429046630859</v>
+      </c>
+      <c r="C120" t="n">
+        <v>55.09999847412109</v>
+      </c>
+      <c r="D120" t="n">
+        <v>268235700</v>
+      </c>
+      <c r="E120" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="F120" t="n">
+        <v>13.30917837539157</v>
+      </c>
+      <c r="G120" t="n">
+        <v>5107812848</v>
+      </c>
+      <c r="H120" t="n">
+        <v>281440480130.8961</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.05251478626610792</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>42369</v>
+      </c>
+      <c r="B121" t="n">
+        <v>40.32536697387695</v>
+      </c>
+      <c r="C121" t="n">
+        <v>54.36000061035156</v>
+      </c>
+      <c r="D121" t="n">
+        <v>340655400</v>
+      </c>
+      <c r="E121" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="F121" t="n">
+        <v>13.13043493003661</v>
+      </c>
+      <c r="G121" t="n">
+        <v>5107812848</v>
+      </c>
+      <c r="H121" t="n">
+        <v>277660709534.8416</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.0666930073863975</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>42400</v>
+      </c>
+      <c r="B122" t="n">
+        <v>37.26162719726562</v>
+      </c>
+      <c r="C122" t="n">
+        <v>50.22999954223633</v>
+      </c>
+      <c r="D122" t="n">
+        <v>472033500</v>
+      </c>
+      <c r="E122" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="F122" t="n">
+        <v>12.13285013097496</v>
+      </c>
+      <c r="G122" t="n">
+        <v>5107812848</v>
+      </c>
+      <c r="H122" t="n">
+        <v>256565437016.8688</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.09241401634063942</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>42429</v>
+      </c>
+      <c r="B123" t="n">
+        <v>35.07558441162109</v>
+      </c>
+      <c r="C123" t="n">
+        <v>46.91999816894531</v>
+      </c>
+      <c r="D123" t="n">
+        <v>473024200</v>
+      </c>
+      <c r="E123" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="F123" t="n">
+        <v>11.38834907013236</v>
+      </c>
+      <c r="G123" t="n">
+        <v>5076712397</v>
+      </c>
+      <c r="H123" t="n">
+        <v>238199336371.502</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.09317529988098713</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>42460</v>
+      </c>
+      <c r="B124" t="n">
+        <v>36.15206146240234</v>
+      </c>
+      <c r="C124" t="n">
+        <v>48.36000061035156</v>
+      </c>
+      <c r="D124" t="n">
+        <v>395938300</v>
+      </c>
+      <c r="E124" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="F124" t="n">
+        <v>11.73786422581349</v>
+      </c>
+      <c r="G124" t="n">
+        <v>5076712397</v>
+      </c>
+      <c r="H124" t="n">
+        <v>245509814617.4993</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.07799108340940748</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>42490</v>
+      </c>
+      <c r="B125" t="n">
+        <v>37.36312484741211</v>
+      </c>
+      <c r="C125" t="n">
+        <v>49.97999954223633</v>
+      </c>
+      <c r="D125" t="n">
+        <v>376851000</v>
+      </c>
+      <c r="E125" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="F125" t="n">
+        <v>12.13106785005736</v>
+      </c>
+      <c r="G125" t="n">
+        <v>5076712397</v>
+      </c>
+      <c r="H125" t="n">
+        <v>253734083278.1255</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.07423130769091704</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>42521</v>
+      </c>
+      <c r="B126" t="n">
+        <v>38.20668029785156</v>
+      </c>
+      <c r="C126" t="n">
+        <v>50.72000122070312</v>
+      </c>
+      <c r="D126" t="n">
+        <v>363734500</v>
+      </c>
+      <c r="E126" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F126" t="n">
+        <v>12.46191676184352</v>
+      </c>
+      <c r="G126" t="n">
+        <v>5077047651</v>
+      </c>
+      <c r="H126" t="n">
+        <v>257507863056.2879</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.07164291631739109</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>42551</v>
+      </c>
+      <c r="B127" t="n">
+        <v>35.65304565429688</v>
+      </c>
+      <c r="C127" t="n">
+        <v>47.33000183105469</v>
+      </c>
+      <c r="D127" t="n">
+        <v>460863700</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F127" t="n">
+        <v>11.62899307888321</v>
+      </c>
+      <c r="G127" t="n">
+        <v>5077047651</v>
+      </c>
+      <c r="H127" t="n">
+        <v>240296674618.1819</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.09077395598389273</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>42582</v>
+      </c>
+      <c r="B128" t="n">
+        <v>36.1351432800293</v>
+      </c>
+      <c r="C128" t="n">
+        <v>47.97000122070312</v>
+      </c>
+      <c r="D128" t="n">
+        <v>353764100</v>
+      </c>
+      <c r="E128" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F128" t="n">
+        <v>11.78624108616784</v>
+      </c>
+      <c r="G128" t="n">
+        <v>5077047651</v>
+      </c>
+      <c r="H128" t="n">
+        <v>243545982016.0379</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.06967909783756332</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>42613</v>
+      </c>
+      <c r="B129" t="n">
+        <v>38.57423782348633</v>
+      </c>
+      <c r="C129" t="n">
+        <v>50.79999923706055</v>
+      </c>
+      <c r="D129" t="n">
+        <v>356092400</v>
+      </c>
+      <c r="E129" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F129" t="n">
+        <v>12.5432096881631</v>
+      </c>
+      <c r="G129" t="n">
+        <v>5045547142</v>
+      </c>
+      <c r="H129" t="n">
+        <v>256313790964.153</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.07057557683602354</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>42643</v>
+      </c>
+      <c r="B130" t="n">
+        <v>33.62338256835938</v>
+      </c>
+      <c r="C130" t="n">
+        <v>44.27999877929688</v>
+      </c>
+      <c r="D130" t="n">
+        <v>760596400</v>
+      </c>
+      <c r="E130" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F130" t="n">
+        <v>10.93333303192516</v>
+      </c>
+      <c r="G130" t="n">
+        <v>5045547142</v>
+      </c>
+      <c r="H130" t="n">
+        <v>223416821288.6448</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.1507460694735493</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>42674</v>
+      </c>
+      <c r="B131" t="n">
+        <v>34.93703079223633</v>
+      </c>
+      <c r="C131" t="n">
+        <v>46.0099983215332</v>
+      </c>
+      <c r="D131" t="n">
+        <v>586021900</v>
+      </c>
+      <c r="E131" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F131" t="n">
+        <v>11.36049341272425</v>
+      </c>
+      <c r="G131" t="n">
+        <v>5045547142</v>
+      </c>
+      <c r="H131" t="n">
+        <v>232145615534.6367</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.1161463531124015</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>42704</v>
+      </c>
+      <c r="B132" t="n">
+        <v>40.51882934570312</v>
+      </c>
+      <c r="C132" t="n">
+        <v>52.91999816894531</v>
+      </c>
+      <c r="D132" t="n">
+        <v>672239000</v>
+      </c>
+      <c r="E132" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="F132" t="n">
+        <v>13.13151319328668</v>
+      </c>
+      <c r="G132" t="n">
+        <v>5022303027</v>
+      </c>
+      <c r="H132" t="n">
+        <v>265780266992.7285</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.1338507446456396</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>42735</v>
+      </c>
+      <c r="B133" t="n">
+        <v>42.19563674926758</v>
+      </c>
+      <c r="C133" t="n">
+        <v>55.11000061035156</v>
+      </c>
+      <c r="D133" t="n">
+        <v>514610900</v>
+      </c>
+      <c r="E133" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="F133" t="n">
+        <v>13.67493811671255</v>
+      </c>
+      <c r="G133" t="n">
+        <v>5022303027</v>
+      </c>
+      <c r="H133" t="n">
+        <v>276779122883.3405</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.1024651235167296</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>42766</v>
+      </c>
+      <c r="B134" t="n">
+        <v>43.12974166870117</v>
+      </c>
+      <c r="C134" t="n">
+        <v>56.33000183105469</v>
+      </c>
+      <c r="D134" t="n">
+        <v>433876600</v>
+      </c>
+      <c r="E134" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="F134" t="n">
+        <v>13.97766794815253</v>
+      </c>
+      <c r="G134" t="n">
+        <v>5022303027</v>
+      </c>
+      <c r="H134" t="n">
+        <v>282906338707.0215</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.0863899684402695</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>42794</v>
+      </c>
+      <c r="B135" t="n">
+        <v>44.61749267578125</v>
+      </c>
+      <c r="C135" t="n">
+        <v>57.88000106811523</v>
+      </c>
+      <c r="D135" t="n">
+        <v>302405300</v>
+      </c>
+      <c r="E135" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="F135" t="n">
+        <v>14.36228314345291</v>
+      </c>
+      <c r="G135" t="n">
+        <v>5022303027</v>
+      </c>
+      <c r="H135" t="n">
+        <v>290690904567.1584</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.06021247590483154</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>42825</v>
+      </c>
+      <c r="B136" t="n">
+        <v>42.90618515014648</v>
+      </c>
+      <c r="C136" t="n">
+        <v>55.65999984741211</v>
+      </c>
+      <c r="D136" t="n">
+        <v>395621300</v>
+      </c>
+      <c r="E136" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F136" t="n">
+        <v>13.94987464847421</v>
+      </c>
+      <c r="G136" t="n">
+        <v>5003367904</v>
+      </c>
+      <c r="H136" t="n">
+        <v>278487456773.1866</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.0790709992930394</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>42855</v>
+      </c>
+      <c r="B137" t="n">
+        <v>41.50322723388672</v>
+      </c>
+      <c r="C137" t="n">
+        <v>53.84000015258789</v>
+      </c>
+      <c r="D137" t="n">
+        <v>413088700</v>
+      </c>
+      <c r="E137" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="F137" t="n">
+        <v>13.49373437408218</v>
+      </c>
+      <c r="G137" t="n">
+        <v>5003367904</v>
+      </c>
+      <c r="H137" t="n">
+        <v>269381328714.8134</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.08256212773594991</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>42886</v>
+      </c>
+      <c r="B138" t="n">
+        <v>39.69847869873047</v>
+      </c>
+      <c r="C138" t="n">
+        <v>51.13999938964844</v>
+      </c>
+      <c r="D138" t="n">
+        <v>397353300</v>
+      </c>
+      <c r="E138" t="n">
+        <v>4</v>
+      </c>
+      <c r="F138" t="n">
+        <v>12.78499984741211</v>
+      </c>
+      <c r="G138" t="n">
+        <v>4997318006</v>
+      </c>
+      <c r="H138" t="n">
+        <v>255562839776.7191</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.07951331084452103</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>42916</v>
+      </c>
+      <c r="B139" t="n">
+        <v>43.01315307617188</v>
+      </c>
+      <c r="C139" t="n">
+        <v>55.40999984741211</v>
+      </c>
+      <c r="D139" t="n">
+        <v>407671900</v>
+      </c>
+      <c r="E139" t="n">
+        <v>4</v>
+      </c>
+      <c r="F139" t="n">
+        <v>13.85249996185303</v>
+      </c>
+      <c r="G139" t="n">
+        <v>4997318006</v>
+      </c>
+      <c r="H139" t="n">
+        <v>276901389949.9298</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.08157813841555234</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>42947</v>
+      </c>
+      <c r="B140" t="n">
+        <v>41.87203979492188</v>
+      </c>
+      <c r="C140" t="n">
+        <v>53.93999862670898</v>
+      </c>
+      <c r="D140" t="n">
+        <v>323918200</v>
+      </c>
+      <c r="E140" t="n">
+        <v>4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>13.48499965667725</v>
+      </c>
+      <c r="G140" t="n">
+        <v>4997318006</v>
+      </c>
+      <c r="H140" t="n">
+        <v>269555326380.8681</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.06481840851654619</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>42978</v>
+      </c>
+      <c r="B141" t="n">
+        <v>39.93212509155273</v>
+      </c>
+      <c r="C141" t="n">
+        <v>51.06999969482422</v>
+      </c>
+      <c r="D141" t="n">
+        <v>394552400</v>
+      </c>
+      <c r="E141" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F141" t="n">
+        <v>12.5788176588237</v>
+      </c>
+      <c r="G141" t="n">
+        <v>4963944641</v>
+      </c>
+      <c r="H141" t="n">
+        <v>253508651300.9943</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.0794836422511989</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>43008</v>
+      </c>
+      <c r="B142" t="n">
+        <v>43.12231063842773</v>
+      </c>
+      <c r="C142" t="n">
+        <v>55.15000152587891</v>
+      </c>
+      <c r="D142" t="n">
+        <v>375336300</v>
+      </c>
+      <c r="E142" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F142" t="n">
+        <v>13.58374421819677</v>
+      </c>
+      <c r="G142" t="n">
+        <v>4963944641</v>
+      </c>
+      <c r="H142" t="n">
+        <v>273761554525.5284</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.07561250721853084</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>43039</v>
+      </c>
+      <c r="B143" t="n">
+        <v>43.89640808105469</v>
+      </c>
+      <c r="C143" t="n">
+        <v>56.13999938964844</v>
+      </c>
+      <c r="D143" t="n">
+        <v>375160400</v>
+      </c>
+      <c r="E143" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F143" t="n">
+        <v>13.82758605656365</v>
+      </c>
+      <c r="G143" t="n">
+        <v>4963944641</v>
+      </c>
+      <c r="H143" t="n">
+        <v>278675849115.9886</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.07557707169039317</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>43069</v>
+      </c>
+      <c r="B144" t="n">
+        <v>44.46292877197266</v>
+      </c>
+      <c r="C144" t="n">
+        <v>56.47000122070312</v>
+      </c>
+      <c r="D144" t="n">
+        <v>368177900</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="F144" t="n">
+        <v>14.59173158157704</v>
+      </c>
+      <c r="G144" t="n">
+        <v>4924261449</v>
+      </c>
+      <c r="H144" t="n">
+        <v>278073050036.0913</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.07476814621099538</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>43100</v>
+      </c>
+      <c r="B145" t="n">
+        <v>47.7698860168457</v>
+      </c>
+      <c r="C145" t="n">
+        <v>60.66999816894531</v>
+      </c>
+      <c r="D145" t="n">
+        <v>422124100</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="F145" t="n">
+        <v>15.67700211083858</v>
+      </c>
+      <c r="G145" t="n">
+        <v>4924261449</v>
+      </c>
+      <c r="H145" t="n">
+        <v>298754933094.238</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.08572333219344463</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>43131</v>
+      </c>
+      <c r="B146" t="n">
+        <v>51.79337310791016</v>
+      </c>
+      <c r="C146" t="n">
+        <v>65.77999877929688</v>
+      </c>
+      <c r="D146" t="n">
+        <v>362611700</v>
+      </c>
+      <c r="E146" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="F146" t="n">
+        <v>16.99741570524467</v>
+      </c>
+      <c r="G146" t="n">
+        <v>4924261449</v>
+      </c>
+      <c r="H146" t="n">
+        <v>323917912104.1587</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.07363778380890758</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>43159</v>
+      </c>
+      <c r="B147" t="n">
+        <v>46.26472854614258</v>
+      </c>
+      <c r="C147" t="n">
+        <v>58.40999984741211</v>
+      </c>
+      <c r="D147" t="n">
+        <v>601421000</v>
+      </c>
+      <c r="E147" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="F147" t="n">
+        <v>15.09302321638556</v>
+      </c>
+      <c r="G147" t="n">
+        <v>4924261449</v>
+      </c>
+      <c r="H147" t="n">
+        <v>287626110484.7073</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.12213425428947</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>43190</v>
+      </c>
+      <c r="B148" t="n">
+        <v>41.51231384277344</v>
+      </c>
+      <c r="C148" t="n">
+        <v>52.40999984741211</v>
+      </c>
+      <c r="D148" t="n">
+        <v>463858700</v>
+      </c>
+      <c r="E148" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>12.78292679205174</v>
+      </c>
+      <c r="G148" t="n">
+        <v>4877753899</v>
+      </c>
+      <c r="H148" t="n">
+        <v>255643081102.3038</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.09509678216752526</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>43220</v>
+      </c>
+      <c r="B149" t="n">
+        <v>41.15587997436523</v>
+      </c>
+      <c r="C149" t="n">
+        <v>51.95999908447266</v>
+      </c>
+      <c r="D149" t="n">
+        <v>435118800</v>
+      </c>
+      <c r="E149" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>12.67317050840797</v>
+      </c>
+      <c r="G149" t="n">
+        <v>4877753899</v>
+      </c>
+      <c r="H149" t="n">
+        <v>253448088126.3229</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.08920474648981466</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>43251</v>
+      </c>
+      <c r="B150" t="n">
+        <v>43.08575057983398</v>
+      </c>
+      <c r="C150" t="n">
+        <v>53.9900016784668</v>
+      </c>
+      <c r="D150" t="n">
+        <v>402405200</v>
+      </c>
+      <c r="E150" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F150" t="n">
+        <v>13.29802997006571</v>
+      </c>
+      <c r="G150" t="n">
+        <v>4872873834</v>
+      </c>
+      <c r="H150" t="n">
+        <v>263086466476.6169</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.08258067286541612</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>43281</v>
+      </c>
+      <c r="B151" t="n">
+        <v>44.24290084838867</v>
+      </c>
+      <c r="C151" t="n">
+        <v>55.43999862670898</v>
+      </c>
+      <c r="D151" t="n">
+        <v>387613300</v>
+      </c>
+      <c r="E151" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F151" t="n">
+        <v>13.65517207554409</v>
+      </c>
+      <c r="G151" t="n">
+        <v>4872873834</v>
+      </c>
+      <c r="H151" t="n">
+        <v>270152118665.0862</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0.07954511304919618</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>43312</v>
+      </c>
+      <c r="B152" t="n">
+        <v>45.71926116943359</v>
+      </c>
+      <c r="C152" t="n">
+        <v>57.29000091552734</v>
+      </c>
+      <c r="D152" t="n">
+        <v>413772800</v>
+      </c>
+      <c r="E152" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F152" t="n">
+        <v>14.11083766392299</v>
+      </c>
+      <c r="G152" t="n">
+        <v>4872873834</v>
+      </c>
+      <c r="H152" t="n">
+        <v>279166946411.1093</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.08491350568384119</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>43343</v>
+      </c>
+      <c r="B153" t="n">
+        <v>47.01043319702148</v>
+      </c>
+      <c r="C153" t="n">
+        <v>58.47999954223633</v>
+      </c>
+      <c r="D153" t="n">
+        <v>374293600</v>
+      </c>
+      <c r="E153" t="n">
+        <v>3.969999999999999</v>
+      </c>
+      <c r="F153" t="n">
+        <v>14.73047847411495</v>
+      </c>
+      <c r="G153" t="n">
+        <v>4816137157</v>
+      </c>
+      <c r="H153" t="n">
+        <v>281647698736.7074</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.0777165574398113</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>43373</v>
+      </c>
+      <c r="B154" t="n">
+        <v>42.25152587890625</v>
+      </c>
+      <c r="C154" t="n">
+        <v>52.56000137329102</v>
+      </c>
+      <c r="D154" t="n">
+        <v>406124000</v>
+      </c>
+      <c r="E154" t="n">
+        <v>3.969999999999999</v>
+      </c>
+      <c r="F154" t="n">
+        <v>13.23929505624459</v>
+      </c>
+      <c r="G154" t="n">
+        <v>4816137157</v>
+      </c>
+      <c r="H154" t="n">
+        <v>253136175585.8779</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.0843256715415009</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>43404</v>
+      </c>
+      <c r="B155" t="n">
+        <v>42.79011154174805</v>
+      </c>
+      <c r="C155" t="n">
+        <v>53.22999954223633</v>
+      </c>
+      <c r="D155" t="n">
+        <v>546018500</v>
+      </c>
+      <c r="E155" t="n">
+        <v>3.969999999999999</v>
+      </c>
+      <c r="F155" t="n">
+        <v>13.4080603380948</v>
+      </c>
+      <c r="G155" t="n">
+        <v>4816137157</v>
+      </c>
+      <c r="H155" t="n">
+        <v>256362978662.4574</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.1133727055938162</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>43434</v>
+      </c>
+      <c r="B156" t="n">
+        <v>43.98717880249023</v>
+      </c>
+      <c r="C156" t="n">
+        <v>54.27999877929688</v>
+      </c>
+      <c r="D156" t="n">
+        <v>419240800</v>
+      </c>
+      <c r="E156" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="F156" t="n">
+        <v>12.74178375100866</v>
+      </c>
+      <c r="G156" t="n">
+        <v>4707244168</v>
+      </c>
+      <c r="H156" t="n">
+        <v>255509207692.8923</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.08906289647136061</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>43465</v>
+      </c>
+      <c r="B157" t="n">
+        <v>37.34210586547852</v>
+      </c>
+      <c r="C157" t="n">
+        <v>46.08000183105469</v>
+      </c>
+      <c r="D157" t="n">
+        <v>597259600</v>
+      </c>
+      <c r="E157" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="F157" t="n">
+        <v>10.81690183827575</v>
+      </c>
+      <c r="G157" t="n">
+        <v>4707244168</v>
+      </c>
+      <c r="H157" t="n">
+        <v>216909819880.6615</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.1268809474682003</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>43496</v>
+      </c>
+      <c r="B158" t="n">
+        <v>39.99477386474609</v>
+      </c>
+      <c r="C158" t="n">
+        <v>48.90999984741211</v>
+      </c>
+      <c r="D158" t="n">
+        <v>470423300</v>
+      </c>
+      <c r="E158" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="F158" t="n">
+        <v>11.48122062145824</v>
+      </c>
+      <c r="G158" t="n">
+        <v>4707244168</v>
+      </c>
+      <c r="H158" t="n">
+        <v>230231311538.6115</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.09993603119165838</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>43524</v>
+      </c>
+      <c r="B159" t="n">
+        <v>40.796142578125</v>
+      </c>
+      <c r="C159" t="n">
+        <v>49.88999938964844</v>
+      </c>
+      <c r="D159" t="n">
+        <v>331490100</v>
+      </c>
+      <c r="E159" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="F159" t="n">
+        <v>11.65654191346926</v>
+      </c>
+      <c r="G159" t="n">
+        <v>4549421815</v>
+      </c>
+      <c r="H159" t="n">
+        <v>226970651573.6033</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.07286422615441739</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>43555</v>
+      </c>
+      <c r="B160" t="n">
+        <v>39.5123176574707</v>
+      </c>
+      <c r="C160" t="n">
+        <v>48.31999969482422</v>
+      </c>
+      <c r="D160" t="n">
+        <v>463436000</v>
+      </c>
+      <c r="E160" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="F160" t="n">
+        <v>11.28971955486547</v>
+      </c>
+      <c r="G160" t="n">
+        <v>4549421815</v>
+      </c>
+      <c r="H160" t="n">
+        <v>219828060712.4266</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.1018670105445037</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>43585</v>
+      </c>
+      <c r="B161" t="n">
+        <v>39.58591461181641</v>
+      </c>
+      <c r="C161" t="n">
+        <v>48.40999984741211</v>
+      </c>
+      <c r="D161" t="n">
+        <v>556953700</v>
+      </c>
+      <c r="E161" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="F161" t="n">
+        <v>11.31074762790002</v>
+      </c>
+      <c r="G161" t="n">
+        <v>4549421815</v>
+      </c>
+      <c r="H161" t="n">
+        <v>220237509369.9633</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.1224229633233075</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>43616</v>
+      </c>
+      <c r="B162" t="n">
+        <v>36.6330680847168</v>
+      </c>
+      <c r="C162" t="n">
+        <v>44.36999893188477</v>
+      </c>
+      <c r="D162" t="n">
+        <v>413827600</v>
+      </c>
+      <c r="E162" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="F162" t="n">
+        <v>9.816371445107247</v>
+      </c>
+      <c r="G162" t="n">
+        <v>4494342882</v>
+      </c>
+      <c r="H162" t="n">
+        <v>199413988873.8639</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.09207744287989107</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>43646</v>
+      </c>
+      <c r="B163" t="n">
+        <v>39.06866073608398</v>
+      </c>
+      <c r="C163" t="n">
+        <v>47.31999969482422</v>
+      </c>
+      <c r="D163" t="n">
+        <v>382936800</v>
+      </c>
+      <c r="E163" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="F163" t="n">
+        <v>10.4690264811558</v>
+      </c>
+      <c r="G163" t="n">
+        <v>4494342882</v>
+      </c>
+      <c r="H163" t="n">
+        <v>212672303804.6754</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.0852041800223288</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>43677</v>
+      </c>
+      <c r="B164" t="n">
+        <v>39.96859359741211</v>
+      </c>
+      <c r="C164" t="n">
+        <v>48.40999984741211</v>
+      </c>
+      <c r="D164" t="n">
+        <v>411656700</v>
+      </c>
+      <c r="E164" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="F164" t="n">
+        <v>10.71017695739206</v>
+      </c>
+      <c r="G164" t="n">
+        <v>4494342882</v>
+      </c>
+      <c r="H164" t="n">
+        <v>217571138231.8377</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.09159441342330588</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>43708</v>
+      </c>
+      <c r="B165" t="n">
+        <v>38.88232803344727</v>
+      </c>
+      <c r="C165" t="n">
+        <v>46.56999969482422</v>
+      </c>
+      <c r="D165" t="n">
+        <v>424863900</v>
+      </c>
+      <c r="E165" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="F165" t="n">
+        <v>9.621900763393434</v>
+      </c>
+      <c r="G165" t="n">
+        <v>4406107022</v>
+      </c>
+      <c r="H165" t="n">
+        <v>205192402669.9028</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.09642614168893876</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>43738</v>
+      </c>
+      <c r="B166" t="n">
+        <v>42.11347198486328</v>
+      </c>
+      <c r="C166" t="n">
+        <v>50.43999862670898</v>
+      </c>
+      <c r="D166" t="n">
+        <v>468177600</v>
+      </c>
+      <c r="E166" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="F166" t="n">
+        <v>10.42148731956797</v>
+      </c>
+      <c r="G166" t="n">
+        <v>4406107022</v>
+      </c>
+      <c r="H166" t="n">
+        <v>222244032138.8128</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0.1062565202484544</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>43769</v>
+      </c>
+      <c r="B167" t="n">
+        <v>43.10702514648438</v>
+      </c>
+      <c r="C167" t="n">
+        <v>51.63000106811523</v>
+      </c>
+      <c r="D167" t="n">
+        <v>463966700</v>
+      </c>
+      <c r="E167" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="F167" t="n">
+        <v>10.66735559258579</v>
+      </c>
+      <c r="G167" t="n">
+        <v>4406107022</v>
+      </c>
+      <c r="H167" t="n">
+        <v>227487310252.09</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0.1053008239889276</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>43799</v>
+      </c>
+      <c r="B168" t="n">
+        <v>45.90501403808594</v>
+      </c>
+      <c r="C168" t="n">
+        <v>54.45999908447266</v>
+      </c>
+      <c r="D168" t="n">
+        <v>328835000</v>
+      </c>
+      <c r="E168" t="n">
+        <v>4.630000000000001</v>
+      </c>
+      <c r="F168" t="n">
+        <v>11.76241880874139</v>
+      </c>
+      <c r="G168" t="n">
+        <v>4229359203</v>
+      </c>
+      <c r="H168" t="n">
+        <v>230330898323.286</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0.0777505490114787</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>43830</v>
+      </c>
+      <c r="B169" t="n">
+        <v>45.34869384765625</v>
+      </c>
+      <c r="C169" t="n">
+        <v>53.79999923706055</v>
+      </c>
+      <c r="D169" t="n">
+        <v>390643100</v>
+      </c>
+      <c r="E169" t="n">
+        <v>4.630000000000001</v>
+      </c>
+      <c r="F169" t="n">
+        <v>11.61987024558543</v>
+      </c>
+      <c r="G169" t="n">
+        <v>4229359203</v>
+      </c>
+      <c r="H169" t="n">
+        <v>227539521894.655</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.09236460684703872</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>43861</v>
+      </c>
+      <c r="B170" t="n">
+        <v>39.56631469726562</v>
+      </c>
+      <c r="C170" t="n">
+        <v>46.93999862670898</v>
+      </c>
+      <c r="D170" t="n">
+        <v>484374600</v>
+      </c>
+      <c r="E170" t="n">
+        <v>4.630000000000001</v>
+      </c>
+      <c r="F170" t="n">
+        <v>10.13822864507753</v>
+      </c>
+      <c r="G170" t="n">
+        <v>4229359203</v>
+      </c>
+      <c r="H170" t="n">
+        <v>198526115180.679</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0.1145267111992805</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>43890</v>
+      </c>
+      <c r="B171" t="n">
+        <v>34.80035018920898</v>
+      </c>
+      <c r="C171" t="n">
+        <v>40.84999847412109</v>
+      </c>
+      <c r="D171" t="n">
+        <v>428717900</v>
+      </c>
+      <c r="E171" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F171" t="n">
+        <v>10.0864193763262</v>
+      </c>
+      <c r="G171" t="n">
+        <v>4099887226</v>
+      </c>
+      <c r="H171" t="n">
+        <v>167480386926.1686</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0.1045682177015081</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>43921</v>
+      </c>
+      <c r="B172" t="n">
+        <v>24.44969749450684</v>
+      </c>
+      <c r="C172" t="n">
+        <v>28.70000076293945</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1116095800</v>
+      </c>
+      <c r="E172" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F172" t="n">
+        <v>7.086419941466532</v>
+      </c>
+      <c r="G172" t="n">
+        <v>4099887226</v>
+      </c>
+      <c r="H172" t="n">
+        <v>117666766514.1657</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0.2722259756127253</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>43951</v>
+      </c>
+      <c r="B173" t="n">
+        <v>24.74786376953125</v>
+      </c>
+      <c r="C173" t="n">
+        <v>29.04999923706055</v>
+      </c>
+      <c r="D173" t="n">
+        <v>868161800</v>
+      </c>
+      <c r="E173" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F173" t="n">
+        <v>7.172839317792728</v>
+      </c>
+      <c r="G173" t="n">
+        <v>4099887226</v>
+      </c>
+      <c r="H173" t="n">
+        <v>119101720787.3343</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.2117526049239677</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>43982</v>
+      </c>
+      <c r="B174" t="n">
+        <v>23.00813293457031</v>
+      </c>
+      <c r="C174" t="n">
+        <v>26.46999931335449</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1055454900</v>
+      </c>
+      <c r="E174" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F174" t="n">
+        <v>9.255244515158914</v>
+      </c>
+      <c r="G174" t="n">
+        <v>4099997545</v>
+      </c>
+      <c r="H174" t="n">
+        <v>108526932200.9051</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0.2574281785332142</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>44012</v>
+      </c>
+      <c r="B175" t="n">
+        <v>22.25191688537598</v>
+      </c>
+      <c r="C175" t="n">
+        <v>25.60000038146973</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1222761300</v>
+      </c>
+      <c r="E175" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F175" t="n">
+        <v>8.951049084429975</v>
+      </c>
+      <c r="G175" t="n">
+        <v>4099997545</v>
+      </c>
+      <c r="H175" t="n">
+        <v>104959938716.0249</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.2982346419917186</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>44043</v>
+      </c>
+      <c r="B176" t="n">
+        <v>21.08716773986816</v>
+      </c>
+      <c r="C176" t="n">
+        <v>24.26000022888184</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1032529700</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F176" t="n">
+        <v>8.482517562546096</v>
+      </c>
+      <c r="G176" t="n">
+        <v>4099997545</v>
+      </c>
+      <c r="H176" t="n">
+        <v>99465941380.11496</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0.2518366629900018</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>44074</v>
+      </c>
+      <c r="B177" t="n">
+        <v>21.07793807983398</v>
+      </c>
+      <c r="C177" t="n">
+        <v>24.14999961853027</v>
+      </c>
+      <c r="D177" t="n">
+        <v>736133000</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="F177" t="n">
+        <v>26.83333290947808</v>
+      </c>
+      <c r="G177" t="n">
+        <v>4120047105</v>
+      </c>
+      <c r="H177" t="n">
+        <v>99499136014.07675</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0.178671015461606</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>44104</v>
+      </c>
+      <c r="B178" t="n">
+        <v>20.51935005187988</v>
+      </c>
+      <c r="C178" t="n">
+        <v>23.51000022888184</v>
+      </c>
+      <c r="D178" t="n">
+        <v>997591200</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="F178" t="n">
+        <v>26.12222247653538</v>
+      </c>
+      <c r="G178" t="n">
+        <v>4120047105</v>
+      </c>
+      <c r="H178" t="n">
+        <v>96862308381.55394</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0.242131018062717</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>44135</v>
+      </c>
+      <c r="B179" t="n">
+        <v>18.72139930725098</v>
+      </c>
+      <c r="C179" t="n">
+        <v>21.45000076293945</v>
+      </c>
+      <c r="D179" t="n">
+        <v>820494900</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="F179" t="n">
+        <v>23.83333418104384</v>
+      </c>
+      <c r="G179" t="n">
+        <v>4120047105</v>
+      </c>
+      <c r="H179" t="n">
+        <v>88375013545.59648</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0.1991469706752297</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>44165</v>
+      </c>
+      <c r="B180" t="n">
+        <v>23.9804744720459</v>
+      </c>
+      <c r="C180" t="n">
+        <v>27.35000038146973</v>
+      </c>
+      <c r="D180" t="n">
+        <v>868248500</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="F180" t="n">
+        <v>68.37500095367434</v>
+      </c>
+      <c r="G180" t="n">
+        <v>4134489571</v>
+      </c>
+      <c r="H180" t="n">
+        <v>113078291344.0326</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0.2100013762496923</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>44196</v>
+      </c>
+      <c r="B181" t="n">
+        <v>26.46181678771973</v>
+      </c>
+      <c r="C181" t="n">
+        <v>30.18000030517578</v>
+      </c>
+      <c r="D181" t="n">
+        <v>737667600</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="F181" t="n">
+        <v>75.45000076293948</v>
+      </c>
+      <c r="G181" t="n">
+        <v>4134489571</v>
+      </c>
+      <c r="H181" t="n">
+        <v>124778896514.5261</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0.1784180579808748</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>44227</v>
+      </c>
+      <c r="B182" t="n">
+        <v>26.19877243041992</v>
+      </c>
+      <c r="C182" t="n">
+        <v>29.8799991607666</v>
+      </c>
+      <c r="D182" t="n">
+        <v>798079600</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="F182" t="n">
+        <v>74.69999790191653</v>
+      </c>
+      <c r="G182" t="n">
+        <v>4134489571</v>
+      </c>
+      <c r="H182" t="n">
+        <v>123538544911.6783</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0.1930297770244394</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>44255</v>
+      </c>
+      <c r="B183" t="n">
+        <v>31.81420135498047</v>
+      </c>
+      <c r="C183" t="n">
+        <v>36.16999816894531</v>
+      </c>
+      <c r="D183" t="n">
+        <v>655506000</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F183" t="n">
+        <v>88.21950772913492</v>
+      </c>
+      <c r="G183" t="n">
+        <v>4134106677</v>
+      </c>
+      <c r="H183" t="n">
+        <v>149530630937.3146</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.1585604947368416</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>44286</v>
+      </c>
+      <c r="B184" t="n">
+        <v>34.36497497558594</v>
+      </c>
+      <c r="C184" t="n">
+        <v>39.06999969482422</v>
+      </c>
+      <c r="D184" t="n">
+        <v>781557400</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F184" t="n">
+        <v>95.2926821824981</v>
+      </c>
+      <c r="G184" t="n">
+        <v>4134106677</v>
+      </c>
+      <c r="H184" t="n">
+        <v>161519546608.7608</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0.18905109641901</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>44316</v>
+      </c>
+      <c r="B185" t="n">
+        <v>39.62483215332031</v>
+      </c>
+      <c r="C185" t="n">
+        <v>45.04999923706055</v>
+      </c>
+      <c r="D185" t="n">
+        <v>634499100</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F185" t="n">
+        <v>109.8780469196599</v>
+      </c>
+      <c r="G185" t="n">
+        <v>4134106677</v>
+      </c>
+      <c r="H185" t="n">
+        <v>186241502644.7769</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0.1534791309401908</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>44347</v>
+      </c>
+      <c r="B186" t="n">
+        <v>41.18337249755859</v>
+      </c>
+      <c r="C186" t="n">
+        <v>46.72000122070312</v>
+      </c>
+      <c r="D186" t="n">
+        <v>526684700</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F186" t="n">
+        <v>32.22069049703664</v>
+      </c>
+      <c r="G186" t="n">
+        <v>4133571501</v>
+      </c>
+      <c r="H186" t="n">
+        <v>193120465572.5836</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0.1274163758562259</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>44377</v>
+      </c>
+      <c r="B187" t="n">
+        <v>39.9228401184082</v>
+      </c>
+      <c r="C187" t="n">
+        <v>45.29000091552734</v>
+      </c>
+      <c r="D187" t="n">
+        <v>607672400</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F187" t="n">
+        <v>31.23448339001886</v>
+      </c>
+      <c r="G187" t="n">
+        <v>4133571501</v>
+      </c>
+      <c r="H187" t="n">
+        <v>187209457064.6877</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0.1470090452900091</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>44408</v>
+      </c>
+      <c r="B188" t="n">
+        <v>40.49580383300781</v>
+      </c>
+      <c r="C188" t="n">
+        <v>45.93999862670898</v>
+      </c>
+      <c r="D188" t="n">
+        <v>560767400</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="F188" t="n">
+        <v>13.16332338874183</v>
+      </c>
+      <c r="G188" t="n">
+        <v>4106410513</v>
+      </c>
+      <c r="H188" t="n">
+        <v>188648493327.9233</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0.1365590211267804</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>44439</v>
+      </c>
+      <c r="B189" t="n">
+        <v>40.45958709716797</v>
+      </c>
+      <c r="C189" t="n">
+        <v>45.70000076293945</v>
+      </c>
+      <c r="D189" t="n">
+        <v>528672200</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="F189" t="n">
+        <v>13.09455609253279</v>
+      </c>
+      <c r="G189" t="n">
+        <v>4106410513</v>
+      </c>
+      <c r="H189" t="n">
+        <v>187662963577.0426</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.1287431440004206</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>44469</v>
+      </c>
+      <c r="B190" t="n">
+        <v>41.08816146850586</v>
+      </c>
+      <c r="C190" t="n">
+        <v>46.40999984741211</v>
+      </c>
+      <c r="D190" t="n">
+        <v>651312400</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="F190" t="n">
+        <v>13.29799422561952</v>
+      </c>
+      <c r="G190" t="n">
+        <v>4106410513</v>
+      </c>
+      <c r="H190" t="n">
+        <v>190578511281.7415</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.158608691931332</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>44500</v>
+      </c>
+      <c r="B191" t="n">
+        <v>45.29348754882812</v>
+      </c>
+      <c r="C191" t="n">
+        <v>51.15999984741211</v>
+      </c>
+      <c r="D191" t="n">
+        <v>516094300</v>
+      </c>
+      <c r="E191" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="F191" t="n">
+        <v>14.65902574424416</v>
+      </c>
+      <c r="G191" t="n">
+        <v>4106410513</v>
+      </c>
+      <c r="H191" t="n">
+        <v>210083961218.4915</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.1256801526214094</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>44530</v>
+      </c>
+      <c r="B192" t="n">
+        <v>42.46438980102539</v>
+      </c>
+      <c r="C192" t="n">
+        <v>47.77999877929688</v>
+      </c>
+      <c r="D192" t="n">
+        <v>501550700</v>
+      </c>
+      <c r="E192" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="F192" t="n">
+        <v>11.26886763662662</v>
+      </c>
+      <c r="G192" t="n">
+        <v>3987232567</v>
+      </c>
+      <c r="H192" t="n">
+        <v>190509967184.0327</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0.1257891762198781</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B193" t="n">
+        <v>42.64214324951172</v>
+      </c>
+      <c r="C193" t="n">
+        <v>47.97999954223633</v>
+      </c>
+      <c r="D193" t="n">
+        <v>518911300</v>
+      </c>
+      <c r="E193" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="F193" t="n">
+        <v>11.31603762788593</v>
+      </c>
+      <c r="G193" t="n">
+        <v>3987232567</v>
+      </c>
+      <c r="H193" t="n">
+        <v>191307416739.4498</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0.1301432237223197</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>44592</v>
+      </c>
+      <c r="B194" t="n">
+        <v>47.81465911865234</v>
+      </c>
+      <c r="C194" t="n">
+        <v>53.79999923706055</v>
+      </c>
+      <c r="D194" t="n">
+        <v>742893200</v>
+      </c>
+      <c r="E194" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="F194" t="n">
+        <v>12.68867906534447</v>
+      </c>
+      <c r="G194" t="n">
+        <v>3987232567</v>
+      </c>
+      <c r="H194" t="n">
+        <v>214513109062.583</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0.1863180006474902</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>44620</v>
+      </c>
+      <c r="B195" t="n">
+        <v>47.64546966552734</v>
+      </c>
+      <c r="C195" t="n">
+        <v>53.36999893188477</v>
+      </c>
+      <c r="D195" t="n">
+        <v>569263200</v>
+      </c>
+      <c r="E195" t="n">
+        <v>4.950000000000001</v>
+      </c>
+      <c r="F195" t="n">
+        <v>10.78181796603732</v>
+      </c>
+      <c r="G195" t="n">
+        <v>3814556833</v>
+      </c>
+      <c r="H195" t="n">
+        <v>203582894102.8237</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0.1492344261528007</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>44651</v>
+      </c>
+      <c r="B196" t="n">
+        <v>43.26211929321289</v>
+      </c>
+      <c r="C196" t="n">
+        <v>48.45999908447266</v>
+      </c>
+      <c r="D196" t="n">
+        <v>754688700</v>
+      </c>
+      <c r="E196" t="n">
+        <v>4.950000000000001</v>
+      </c>
+      <c r="F196" t="n">
+        <v>9.789898804943968</v>
+      </c>
+      <c r="G196" t="n">
+        <v>3814556833</v>
+      </c>
+      <c r="H196" t="n">
+        <v>184853420634.8489</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0.1978443979314018</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>44681</v>
+      </c>
+      <c r="B197" t="n">
+        <v>38.95018768310547</v>
+      </c>
+      <c r="C197" t="n">
+        <v>43.63000106811523</v>
+      </c>
+      <c r="D197" t="n">
+        <v>521880200</v>
+      </c>
+      <c r="E197" t="n">
+        <v>4.950000000000001</v>
+      </c>
+      <c r="F197" t="n">
+        <v>8.814141629922268</v>
+      </c>
+      <c r="G197" t="n">
+        <v>3814556833</v>
+      </c>
+      <c r="H197" t="n">
+        <v>166429118698.1763</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0.1368127997163858</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>44712</v>
+      </c>
+      <c r="B198" t="n">
+        <v>41.08402633666992</v>
+      </c>
+      <c r="C198" t="n">
+        <v>45.77000045776367</v>
+      </c>
+      <c r="D198" t="n">
+        <v>548344800</v>
+      </c>
+      <c r="E198" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F198" t="n">
+        <v>9.57531390329784</v>
+      </c>
+      <c r="G198" t="n">
+        <v>3790352243</v>
+      </c>
+      <c r="H198" t="n">
+        <v>173484423897.1956</v>
+      </c>
+      <c r="I198" t="n">
+        <v>0.1446685597658318</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B199" t="n">
+        <v>35.15974044799805</v>
+      </c>
+      <c r="C199" t="n">
+        <v>39.16999816894531</v>
+      </c>
+      <c r="D199" t="n">
+        <v>503139500</v>
+      </c>
+      <c r="E199" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F199" t="n">
+        <v>8.194560286390232</v>
+      </c>
+      <c r="G199" t="n">
+        <v>3790352243</v>
+      </c>
+      <c r="H199" t="n">
+        <v>148468090417.9678</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0.1327421484188429</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>44773</v>
+      </c>
+      <c r="B200" t="n">
+        <v>39.37855529785156</v>
+      </c>
+      <c r="C200" t="n">
+        <v>43.86999893188477</v>
+      </c>
+      <c r="D200" t="n">
+        <v>377913800</v>
+      </c>
+      <c r="E200" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F200" t="n">
+        <v>9.177824044327357</v>
+      </c>
+      <c r="G200" t="n">
+        <v>3790352243</v>
+      </c>
+      <c r="H200" t="n">
+        <v>166282748851.877</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0.09970413718089895</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>44804</v>
+      </c>
+      <c r="B201" t="n">
+        <v>39.50496292114258</v>
+      </c>
+      <c r="C201" t="n">
+        <v>43.70999908447266</v>
+      </c>
+      <c r="D201" t="n">
+        <v>308752700</v>
+      </c>
+      <c r="E201" t="n">
+        <v>4.140000000000001</v>
+      </c>
+      <c r="F201" t="n">
+        <v>10.55797079335088</v>
+      </c>
+      <c r="G201" t="n">
+        <v>3793049509</v>
+      </c>
+      <c r="H201" t="n">
+        <v>165794190565.7495</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0.08139959662203292</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>44834</v>
+      </c>
+      <c r="B202" t="n">
+        <v>36.35071182250977</v>
+      </c>
+      <c r="C202" t="n">
+        <v>40.22000122070312</v>
+      </c>
+      <c r="D202" t="n">
+        <v>354330500</v>
+      </c>
+      <c r="E202" t="n">
+        <v>4.140000000000001</v>
+      </c>
+      <c r="F202" t="n">
+        <v>9.714976140266455</v>
+      </c>
+      <c r="G202" t="n">
+        <v>3793049509</v>
+      </c>
+      <c r="H202" t="n">
+        <v>152556455882.1674</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0.09341573295029722</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>44865</v>
+      </c>
+      <c r="B203" t="n">
+        <v>41.56562423706055</v>
+      </c>
+      <c r="C203" t="n">
+        <v>45.9900016784668</v>
+      </c>
+      <c r="D203" t="n">
+        <v>383039100</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="F203" t="n">
+        <v>12.03926745509602</v>
+      </c>
+      <c r="G203" t="n">
+        <v>3810490898</v>
+      </c>
+      <c r="H203" t="n">
+        <v>175244482794.8025</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0.1005222450999803</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>44895</v>
+      </c>
+      <c r="B204" t="n">
+        <v>43.61617660522461</v>
+      </c>
+      <c r="C204" t="n">
+        <v>47.95000076293945</v>
+      </c>
+      <c r="D204" t="n">
+        <v>348895000</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="F204" t="n">
+        <v>12.55235622066478</v>
+      </c>
+      <c r="G204" t="n">
+        <v>3810490898</v>
+      </c>
+      <c r="H204" t="n">
+        <v>182713041466.2738</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0.09156169358208502</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B205" t="n">
+        <v>37.55812072753906</v>
+      </c>
+      <c r="C205" t="n">
+        <v>41.29000091552734</v>
+      </c>
+      <c r="D205" t="n">
+        <v>414604800</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="F205" t="n">
+        <v>10.80890076322705</v>
+      </c>
+      <c r="G205" t="n">
+        <v>3810490898</v>
+      </c>
+      <c r="H205" t="n">
+        <v>157335172667.0286</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0.1088061383948226</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>44957</v>
+      </c>
+      <c r="B206" t="n">
+        <v>42.63378524780273</v>
+      </c>
+      <c r="C206" t="n">
+        <v>46.86999893188477</v>
+      </c>
+      <c r="D206" t="n">
+        <v>398335300</v>
+      </c>
+      <c r="E206" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="F206" t="n">
+        <v>12.26963322824208</v>
+      </c>
+      <c r="G206" t="n">
+        <v>3810490898</v>
+      </c>
+      <c r="H206" t="n">
+        <v>178597704319.2166</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0.1045364785437679</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>44985</v>
+      </c>
+      <c r="B207" t="n">
+        <v>42.814208984375</v>
+      </c>
+      <c r="C207" t="n">
+        <v>46.77000045776367</v>
+      </c>
+      <c r="D207" t="n">
+        <v>314575300</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="F207" t="n">
+        <v>14.89490460438334</v>
+      </c>
+      <c r="G207" t="n">
+        <v>3793867540</v>
+      </c>
+      <c r="H207" t="n">
+        <v>177439186582.4948</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0.0829167852286166</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B208" t="n">
+        <v>34.21841049194336</v>
+      </c>
+      <c r="C208" t="n">
+        <v>37.38000106811523</v>
+      </c>
+      <c r="D208" t="n">
+        <v>730423100</v>
+      </c>
+      <c r="E208" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="F208" t="n">
+        <v>11.9044589388902</v>
+      </c>
+      <c r="G208" t="n">
+        <v>3793867540</v>
+      </c>
+      <c r="H208" t="n">
+        <v>141814772697.4877</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0.1925273068442447</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>45046</v>
+      </c>
+      <c r="B209" t="n">
+        <v>36.38795852661133</v>
+      </c>
+      <c r="C209" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="D209" t="n">
+        <v>450940100</v>
+      </c>
+      <c r="E209" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="F209" t="n">
+        <v>12.65923566878981</v>
+      </c>
+      <c r="G209" t="n">
+        <v>3793867540</v>
+      </c>
+      <c r="H209" t="n">
+        <v>150806234715</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0.1188602646891568</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>45077</v>
+      </c>
+      <c r="B210" t="n">
+        <v>36.72795486450195</v>
+      </c>
+      <c r="C210" t="n">
+        <v>39.81000137329102</v>
+      </c>
+      <c r="D210" t="n">
+        <v>538516100</v>
+      </c>
+      <c r="E210" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="F210" t="n">
+        <v>11.40687718432407</v>
+      </c>
+      <c r="G210" t="n">
+        <v>3752223519</v>
+      </c>
+      <c r="H210" t="n">
+        <v>149376023444.2849</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0.143519195291308</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B211" t="n">
+        <v>39.37577056884766</v>
+      </c>
+      <c r="C211" t="n">
+        <v>42.68000030517578</v>
+      </c>
+      <c r="D211" t="n">
+        <v>363195000</v>
+      </c>
+      <c r="E211" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="F211" t="n">
+        <v>12.22922644847444</v>
+      </c>
+      <c r="G211" t="n">
+        <v>3752223519</v>
+      </c>
+      <c r="H211" t="n">
+        <v>160144900936.0078</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0.09679460676073866</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B212" t="n">
+        <v>42.58634948730469</v>
+      </c>
+      <c r="C212" t="n">
+        <v>46.15999984741211</v>
+      </c>
+      <c r="D212" t="n">
+        <v>340830500</v>
+      </c>
+      <c r="E212" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="F212" t="n">
+        <v>13.22636098779716</v>
+      </c>
+      <c r="G212" t="n">
+        <v>3752223519</v>
+      </c>
+      <c r="H212" t="n">
+        <v>173202637064.4961</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0.09083427420412157</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B213" t="n">
+        <v>38.39132308959961</v>
+      </c>
+      <c r="C213" t="n">
+        <v>41.29000091552734</v>
+      </c>
+      <c r="D213" t="n">
+        <v>284173100</v>
+      </c>
+      <c r="E213" t="n">
+        <v>4</v>
+      </c>
+      <c r="F213" t="n">
+        <v>10.32250022888184</v>
+      </c>
+      <c r="G213" t="n">
+        <v>3752223519</v>
+      </c>
+      <c r="H213" t="n">
+        <v>154929312534.7732</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0.07573458738826268</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B214" t="n">
+        <v>37.99149703979492</v>
+      </c>
+      <c r="C214" t="n">
+        <v>40.86000061035156</v>
+      </c>
+      <c r="D214" t="n">
+        <v>333548000</v>
+      </c>
+      <c r="E214" t="n">
+        <v>4</v>
+      </c>
+      <c r="F214" t="n">
+        <v>10.21500015258789</v>
+      </c>
+      <c r="G214" t="n">
+        <v>3752223519</v>
+      </c>
+      <c r="H214" t="n">
+        <v>153315855276.5155</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0.08889342500813849</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="B215" t="n">
+        <v>36.97802734375</v>
+      </c>
+      <c r="C215" t="n">
+        <v>39.77000045776367</v>
+      </c>
+      <c r="D215" t="n">
+        <v>341744500</v>
+      </c>
+      <c r="E215" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="F215" t="n">
+        <v>8.589632928242693</v>
+      </c>
+      <c r="G215" t="n">
+        <v>3631639714</v>
+      </c>
+      <c r="H215" t="n">
+        <v>144430313088.2127</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0.0941019833775284</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>45260</v>
+      </c>
+      <c r="B216" t="n">
+        <v>41.82925415039062</v>
+      </c>
+      <c r="C216" t="n">
+        <v>44.59000015258789</v>
+      </c>
+      <c r="D216" t="n">
+        <v>328148500</v>
+      </c>
+      <c r="E216" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="F216" t="n">
+        <v>9.630669579392633</v>
+      </c>
+      <c r="G216" t="n">
+        <v>3631639714</v>
+      </c>
+      <c r="H216" t="n">
+        <v>161934815401.4042</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0.09035821993436874</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B217" t="n">
+        <v>46.17259979248047</v>
+      </c>
+      <c r="C217" t="n">
+        <v>49.22000122070312</v>
+      </c>
+      <c r="D217" t="n">
+        <v>382836700</v>
+      </c>
+      <c r="E217" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="F217" t="n">
+        <v>10.63066981008707</v>
+      </c>
+      <c r="G217" t="n">
+        <v>3631639714</v>
+      </c>
+      <c r="H217" t="n">
+        <v>178749311156.2339</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0.1054170375227921</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>45322</v>
+      </c>
+      <c r="B218" t="n">
+        <v>47.07315444946289</v>
+      </c>
+      <c r="C218" t="n">
+        <v>50.18000030517578</v>
+      </c>
+      <c r="D218" t="n">
+        <v>388441000</v>
+      </c>
+      <c r="E218" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="F218" t="n">
+        <v>10.83801302487598</v>
+      </c>
+      <c r="G218" t="n">
+        <v>3631639714</v>
+      </c>
+      <c r="H218" t="n">
+        <v>182235681956.8085</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0.1069602247443646</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>45351</v>
+      </c>
+      <c r="B219" t="n">
+        <v>52.51448440551758</v>
+      </c>
+      <c r="C219" t="n">
+        <v>55.59000015258789</v>
+      </c>
+      <c r="D219" t="n">
+        <v>395337800</v>
+      </c>
+      <c r="E219" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="F219" t="n">
+        <v>11.50931680177803</v>
+      </c>
+      <c r="G219" t="n">
+        <v>3577443489</v>
+      </c>
+      <c r="H219" t="n">
+        <v>198870084099.3846</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0.1105084681884125</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B220" t="n">
+        <v>54.75336456298828</v>
+      </c>
+      <c r="C220" t="n">
+        <v>57.95999908447266</v>
+      </c>
+      <c r="D220" t="n">
+        <v>384218700</v>
+      </c>
+      <c r="E220" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="F220" t="n">
+        <v>11.99999981044983</v>
+      </c>
+      <c r="G220" t="n">
+        <v>3577443489</v>
+      </c>
+      <c r="H220" t="n">
+        <v>207348621347.1927</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0.1074003548012439</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>45412</v>
+      </c>
+      <c r="B221" t="n">
+        <v>56.03812789916992</v>
+      </c>
+      <c r="C221" t="n">
+        <v>59.31999969482422</v>
+      </c>
+      <c r="D221" t="n">
+        <v>413690600</v>
+      </c>
+      <c r="E221" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="F221" t="n">
+        <v>12.28157343578141</v>
+      </c>
+      <c r="G221" t="n">
+        <v>3577443489</v>
+      </c>
+      <c r="H221" t="n">
+        <v>212213946675.7309</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0.1156386121184093</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="B222" t="n">
+        <v>56.93035507202148</v>
+      </c>
+      <c r="C222" t="n">
+        <v>59.91999816894531</v>
+      </c>
+      <c r="D222" t="n">
+        <v>342804600</v>
+      </c>
+      <c r="E222" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F222" t="n">
+        <v>12.48333295186361</v>
+      </c>
+      <c r="G222" t="n">
+        <v>3486315358</v>
+      </c>
+      <c r="H222" t="n">
+        <v>208900009867.7259</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0.09832862629978983</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B223" t="n">
+        <v>56.42679214477539</v>
+      </c>
+      <c r="C223" t="n">
+        <v>59.38999938964844</v>
+      </c>
+      <c r="D223" t="n">
+        <v>377118800</v>
+      </c>
+      <c r="E223" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F223" t="n">
+        <v>12.37291653951009</v>
+      </c>
+      <c r="G223" t="n">
+        <v>3486315358</v>
+      </c>
+      <c r="H223" t="n">
+        <v>207052266983.742</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0.1081711667691308</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>45504</v>
+      </c>
+      <c r="B224" t="n">
+        <v>56.3792839050293</v>
+      </c>
+      <c r="C224" t="n">
+        <v>59.34000015258789</v>
+      </c>
+      <c r="D224" t="n">
+        <v>343211000</v>
+      </c>
+      <c r="E224" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F224" t="n">
+        <v>12.36250003178914</v>
+      </c>
+      <c r="G224" t="n">
+        <v>3486315358</v>
+      </c>
+      <c r="H224" t="n">
+        <v>206877953875.6895</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0.09844519636252597</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>45535</v>
+      </c>
+      <c r="B225" t="n">
+        <v>55.97708511352539</v>
+      </c>
+      <c r="C225" t="n">
+        <v>58.47000122070312</v>
+      </c>
+      <c r="D225" t="n">
+        <v>348723100</v>
+      </c>
+      <c r="E225" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="F225" t="n">
+        <v>11.98155762719326</v>
+      </c>
+      <c r="G225" t="n">
+        <v>3403770246</v>
+      </c>
+      <c r="H225" t="n">
+        <v>199018450438.613</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0.1024520090360999</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B226" t="n">
+        <v>54.08150482177734</v>
+      </c>
+      <c r="C226" t="n">
+        <v>56.4900016784668</v>
+      </c>
+      <c r="D226" t="n">
+        <v>420231200</v>
+      </c>
+      <c r="E226" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="F226" t="n">
+        <v>11.57582001607926</v>
+      </c>
+      <c r="G226" t="n">
+        <v>3403770246</v>
+      </c>
+      <c r="H226" t="n">
+        <v>192278986909.6553</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0.1234605069169525</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>45596</v>
+      </c>
+      <c r="B227" t="n">
+        <v>62.15208053588867</v>
+      </c>
+      <c r="C227" t="n">
+        <v>64.91999816894531</v>
+      </c>
+      <c r="D227" t="n">
+        <v>387173600</v>
+      </c>
+      <c r="E227" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F227" t="n">
+        <v>13.46887928816293</v>
+      </c>
+      <c r="G227" t="n">
+        <v>3329490659</v>
+      </c>
+      <c r="H227" t="n">
+        <v>216150527485.8005</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0.1162861349237983</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B228" t="n">
+        <v>73.34261322021484</v>
+      </c>
+      <c r="C228" t="n">
+        <v>76.16999816894531</v>
+      </c>
+      <c r="D228" t="n">
+        <v>382978600</v>
+      </c>
+      <c r="E228" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F228" t="n">
+        <v>15.80290418442849</v>
+      </c>
+      <c r="G228" t="n">
+        <v>3329490659</v>
+      </c>
+      <c r="H228" t="n">
+        <v>253607297399.5505</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0.1150261824476859</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B229" t="n">
+        <v>67.63272094726562</v>
+      </c>
+      <c r="C229" t="n">
+        <v>70.23999786376953</v>
+      </c>
+      <c r="D229" t="n">
+        <v>322967900</v>
+      </c>
+      <c r="E229" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F229" t="n">
+        <v>14.57261366468247</v>
+      </c>
+      <c r="G229" t="n">
+        <v>3329490659</v>
+      </c>
+      <c r="H229" t="n">
+        <v>233863416775.6006</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0.09700219435275491</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B230" t="n">
+        <v>75.875</v>
+      </c>
+      <c r="C230" t="n">
+        <v>78.80000305175781</v>
+      </c>
+      <c r="D230" t="n">
+        <v>300692400</v>
+      </c>
+      <c r="E230" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F230" t="n">
+        <v>16.3485483509871</v>
+      </c>
+      <c r="G230" t="n">
+        <v>3329490659</v>
+      </c>
+      <c r="H230" t="n">
+        <v>262363874089.9991</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0.09031183168728632</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B231" t="n">
+        <v>75.78512573242188</v>
+      </c>
+      <c r="C231" t="n">
+        <v>78.31999969482422</v>
+      </c>
+      <c r="D231" t="n">
+        <v>298858000</v>
+      </c>
+      <c r="E231" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="F231" t="n">
+        <v>14.58472992454827</v>
+      </c>
+      <c r="G231" t="n">
+        <v>3288186582</v>
+      </c>
+      <c r="H231" t="n">
+        <v>257530772098.7651</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0.09088839472674425</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B232" t="n">
+        <v>69.46646118164062</v>
+      </c>
+      <c r="C232" t="n">
+        <v>71.79000091552734</v>
+      </c>
+      <c r="D232" t="n">
+        <v>363280500</v>
+      </c>
+      <c r="E232" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="F232" t="n">
+        <v>13.36871525428815</v>
+      </c>
+      <c r="G232" t="n">
+        <v>3288186582</v>
+      </c>
+      <c r="H232" t="n">
+        <v>236058917732.2047</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0.110480500707791</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B233" t="n">
+        <v>68.71171569824219</v>
+      </c>
+      <c r="C233" t="n">
+        <v>71.01000213623047</v>
+      </c>
+      <c r="D233" t="n">
+        <v>493519900</v>
+      </c>
+      <c r="E233" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="F233" t="n">
+        <v>12.77158311802706</v>
+      </c>
+      <c r="G233" t="n">
+        <v>3254182446</v>
+      </c>
+      <c r="H233" t="n">
+        <v>231079502442.1437</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0.1516571084103254</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B234" t="n">
+        <v>72.75667572021484</v>
+      </c>
+      <c r="C234" t="n">
+        <v>74.77999877929688</v>
+      </c>
+      <c r="D234" t="n">
+        <v>305735400</v>
+      </c>
+      <c r="E234" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="F234" t="n">
+        <v>13.44964006821886</v>
+      </c>
+      <c r="G234" t="n">
+        <v>3254182446</v>
+      </c>
+      <c r="H234" t="n">
+        <v>243347759339.4893</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0.09395152394599328</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B235" t="n">
+        <v>77.95219421386719</v>
+      </c>
+      <c r="C235" t="n">
+        <v>80.12000274658203</v>
+      </c>
+      <c r="D235" t="n">
+        <v>356076100</v>
+      </c>
+      <c r="E235" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="F235" t="n">
+        <v>14.41007243643562</v>
+      </c>
+      <c r="G235" t="n">
+        <v>3254182446</v>
+      </c>
+      <c r="H235" t="n">
+        <v>260725106511.399</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0.1094210622510377</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B236" t="n">
+        <v>78.44838714599609</v>
+      </c>
+      <c r="C236" t="n">
+        <v>80.62999725341797</v>
+      </c>
+      <c r="D236" t="n">
+        <v>417623500</v>
+      </c>
+      <c r="E236" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="F236" t="n">
+        <v>14.50179806716151</v>
+      </c>
+      <c r="G236" t="n">
+        <v>3254182446</v>
+      </c>
+      <c r="H236" t="n">
+        <v>262384721683.101</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0.1283343841133854</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B237" t="n">
+        <v>80.42617797851562</v>
+      </c>
+      <c r="C237" t="n">
+        <v>82.18000030517578</v>
+      </c>
+      <c r="D237" t="n">
+        <v>284526700</v>
+      </c>
+      <c r="E237" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="F237" t="n">
+        <v>14.09605494085348</v>
+      </c>
+      <c r="G237" t="n">
+        <v>3203441209</v>
+      </c>
+      <c r="H237" t="n">
+        <v>263258799533.2327</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0.0888190796823829</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B238" t="n">
+        <v>82.03116607666016</v>
+      </c>
+      <c r="C238" t="n">
+        <v>83.81999969482422</v>
+      </c>
+      <c r="D238" t="n">
+        <v>296633400</v>
+      </c>
+      <c r="E238" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="F238" t="n">
+        <v>14.37735843822028</v>
+      </c>
+      <c r="G238" t="n">
+        <v>3203441209</v>
+      </c>
+      <c r="H238" t="n">
+        <v>268512441160.7673</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0.0925983592789575</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B239" t="n">
+        <v>85.11395263671875</v>
+      </c>
+      <c r="C239" t="n">
+        <v>86.97000122070312</v>
+      </c>
+      <c r="D239" t="n">
+        <v>366280200</v>
+      </c>
+      <c r="E239" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="F239" t="n">
+        <v>14.32784204624434</v>
+      </c>
+      <c r="G239" t="n">
+        <v>3139084542</v>
+      </c>
+      <c r="H239" t="n">
+        <v>273006186449.6303</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0.1166837640398919</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B240" t="n">
+        <v>84.45958709716797</v>
+      </c>
+      <c r="C240" t="n">
+        <v>85.84999847412109</v>
+      </c>
+      <c r="D240" t="n">
+        <v>276745000</v>
+      </c>
+      <c r="E240" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="F240" t="n">
+        <v>14.14332759046476</v>
+      </c>
+      <c r="G240" t="n">
+        <v>3139084542</v>
+      </c>
+      <c r="H240" t="n">
+        <v>269490403140.8371</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0.08816105342090529</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B241" t="n">
+        <v>91.69053649902344</v>
+      </c>
+      <c r="C241" t="n">
+        <v>93.19999694824219</v>
+      </c>
+      <c r="D241" t="n">
+        <v>282602400</v>
+      </c>
+      <c r="E241" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="F241" t="n">
+        <v>15.35420048570711</v>
+      </c>
+      <c r="G241" t="n">
+        <v>3139084542</v>
+      </c>
+      <c r="H241" t="n">
+        <v>292562669734.6742</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0.09002701144835876</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B242" t="n">
+        <v>89.02444458007812</v>
+      </c>
+      <c r="C242" t="n">
+        <v>90.48999786376953</v>
+      </c>
+      <c r="D242" t="n">
+        <v>349902000</v>
+      </c>
+      <c r="E242" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="F242" t="n">
+        <v>14.90774264642002</v>
+      </c>
+      <c r="G242" t="n">
+        <v>3139084542</v>
+      </c>
+      <c r="H242" t="n">
+        <v>284055753499.772</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0.1114662556291228</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B243" t="n">
+        <v>80.52467346191406</v>
+      </c>
+      <c r="C243" t="n">
+        <v>81.44999694824219</v>
+      </c>
+      <c r="D243" t="n">
+        <v>304856000</v>
+      </c>
+      <c r="E243" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="F243" t="n">
+        <v>13.01118162112495</v>
+      </c>
+      <c r="G243" t="n">
+        <v>3085635641</v>
+      </c>
+      <c r="H243" t="n">
+        <v>251325013542.8373</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0.09879844397350866</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B244" t="n">
+        <v>78.70558166503906</v>
+      </c>
+      <c r="C244" t="n">
+        <v>79.61000061035156</v>
+      </c>
+      <c r="D244" t="n">
+        <v>420231100</v>
+      </c>
+      <c r="E244" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="F244" t="n">
+        <v>12.71725249366638</v>
+      </c>
+      <c r="G244" t="n">
+        <v>3085635641</v>
+      </c>
+      <c r="H244" t="n">
+        <v>245647455263.3325</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0.1361894756517041</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B245" t="n">
+        <v>81.29581451416016</v>
+      </c>
+      <c r="C245" t="n">
+        <v>82.23000335693359</v>
+      </c>
+      <c r="D245" t="n">
+        <v>341123100</v>
+      </c>
+      <c r="E245" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="F245" t="n">
+        <v>12.70942864867598</v>
+      </c>
+      <c r="G245" t="n">
+        <v>3060189494</v>
+      </c>
+      <c r="H245" t="n">
+        <v>251639392364.4729</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0.1114712342712199</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B246" t="n">
+        <v>77.09737396240234</v>
+      </c>
+      <c r="C246" t="n">
+        <v>77.54000091552734</v>
+      </c>
+      <c r="D246" t="n">
+        <v>344548100</v>
+      </c>
+      <c r="E246" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="F246" t="n">
+        <v>11.9845441909625</v>
+      </c>
+      <c r="G246" t="n">
+        <v>3060189494</v>
+      </c>
+      <c r="H246" t="n">
+        <v>237287096166.4471</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0.1125904460085046</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B247" t="n">
+        <v>82.16825866699219</v>
+      </c>
+      <c r="C247" t="n">
+        <v>82.63999938964844</v>
+      </c>
+      <c r="D247" t="n">
+        <v>336836100</v>
+      </c>
+      <c r="E247" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="F247" t="n">
+        <v>12.77279743271228</v>
+      </c>
+      <c r="G247" t="n">
+        <v>3060189494</v>
+      </c>
+      <c r="H247" t="n">
+        <v>252894057916.3686</v>
+      </c>
+      <c r="I247" t="n">
+        <v>0.1100703406310041</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B248" t="n">
+        <v>85.95650482177734</v>
+      </c>
+      <c r="C248" t="n">
+        <v>86.44999694824219</v>
+      </c>
+      <c r="D248" t="n">
+        <v>357033000</v>
+      </c>
+      <c r="E248" t="n">
+        <v>6.869999999999999</v>
+      </c>
+      <c r="F248" t="n">
+        <v>12.58369679013715</v>
+      </c>
+      <c r="G248" t="n">
+        <v>3023999336</v>
+      </c>
+      <c r="H248" t="n">
+        <v>261424733368.6864</v>
+      </c>
+      <c r="I248" t="n">
+        <v>0.1180664941786217</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B249" t="n">
+        <v>86.38999938964844</v>
+      </c>
+      <c r="C249" t="n">
+        <v>86.38999938964844</v>
+      </c>
+      <c r="D249" t="n">
+        <v>244764200</v>
+      </c>
+      <c r="E249" t="n">
+        <v>6.869999999999999</v>
+      </c>
+      <c r="F249" t="n">
+        <v>12.57496352105509</v>
+      </c>
+      <c r="G249" t="n">
+        <v>3023999336</v>
+      </c>
+      <c r="H249" t="n">
+        <v>261243300791.3373</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0.08094056010070499</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B250" t="n">
+        <v>82.18000030517578</v>
+      </c>
+      <c r="C250" t="n">
+        <v>82.18000030517578</v>
+      </c>
+      <c r="D250" t="n">
+        <v>246764800</v>
+      </c>
+      <c r="E250" t="n">
+        <v>6.869999999999999</v>
+      </c>
+      <c r="F250" t="n">
+        <v>11.96215433845354</v>
+      </c>
+      <c r="G250" t="n">
+        <v>3023999336</v>
+      </c>
+      <c r="H250" t="n">
+        <v>248512266355.3314</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0.08160213432004537</v>
       </c>
     </row>
   </sheetData>
@@ -469,75 +7241,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -573,13 +7345,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -615,13 +7387,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -657,13 +7429,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -699,13 +7471,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -741,13 +7513,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -783,13 +7555,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -825,13 +7597,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -867,13 +7639,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -900,7 +7672,7 @@
       <c r="I10" t="n">
         <v>2.21</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -913,13 +7685,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -946,7 +7718,7 @@
       <c r="I11" t="n">
         <v>2.43</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K11" t="n">
@@ -959,13 +7731,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -992,7 +7764,7 @@
       <c r="I12" t="n">
         <v>2.58</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K12" t="n">
@@ -1005,13 +7777,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1038,7 +7810,7 @@
       <c r="I13" t="n">
         <v>2.7</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="K13" t="n">
@@ -1051,13 +7823,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -1084,7 +7856,7 @@
       <c r="I14" t="n">
         <v>2.82</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="K14" t="n">
@@ -1097,13 +7869,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -1130,7 +7902,7 @@
       <c r="I15" t="n">
         <v>2.9</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K15" t="n">
@@ -1143,13 +7915,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -1176,7 +7948,7 @@
       <c r="I16" t="n">
         <v>3.02</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="K16" t="n">
@@ -1189,13 +7961,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -1222,7 +7994,7 @@
       <c r="I17" t="n">
         <v>3.18</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K17" t="n">
@@ -1235,13 +8007,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -1268,7 +8040,7 @@
       <c r="I18" t="n">
         <v>3.36</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="K18" t="n">
@@ -1281,13 +8053,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -1314,7 +8086,7 @@
       <c r="I19" t="n">
         <v>3.53</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="K19" t="n">
@@ -1327,13 +8099,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -1360,7 +8132,7 @@
       <c r="I20" t="n">
         <v>3.69</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="K20" t="n">
@@ -1373,13 +8145,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -1406,7 +8178,7 @@
       <c r="I21" t="n">
         <v>3.8</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="K21" t="n">
@@ -1419,13 +8191,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -1452,7 +8224,7 @@
       <c r="I22" t="n">
         <v>3.89</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="K22" t="n">
@@ -1465,13 +8237,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -1498,7 +8270,7 @@
       <c r="I23" t="n">
         <v>4.02</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="K23" t="n">
@@ -1511,13 +8283,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -1544,7 +8316,7 @@
       <c r="I24" t="n">
         <v>4.050000000000001</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="K24" t="n">
@@ -1557,13 +8329,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -1590,7 +8362,7 @@
       <c r="I25" t="n">
         <v>4.08</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="K25" t="n">
@@ -1603,13 +8375,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -1636,7 +8408,7 @@
       <c r="I26" t="n">
         <v>4.1</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K26" t="n">
@@ -1649,13 +8421,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -1682,7 +8454,7 @@
       <c r="I27" t="n">
         <v>4.09</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K27" t="n">
@@ -1695,13 +8467,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -1728,7 +8500,7 @@
       <c r="I28" t="n">
         <v>4.109999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K28" t="n">
@@ -1741,13 +8513,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -1774,7 +8546,7 @@
       <c r="I29" t="n">
         <v>4.14</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K29" t="n">
@@ -1787,13 +8559,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -1820,7 +8592,7 @@
       <c r="I30" t="n">
         <v>4.12</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="K30" t="n">
@@ -1833,13 +8605,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -1866,7 +8638,7 @@
       <c r="I31" t="n">
         <v>4.07</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K31" t="n">
@@ -1879,13 +8651,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -1912,7 +8684,7 @@
       <c r="I32" t="n">
         <v>4.05</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K32" t="n">
@@ -1925,13 +8697,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -1958,7 +8730,7 @@
       <c r="I33" t="n">
         <v>4.03</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K33" t="n">
@@ -1971,13 +8743,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -2004,7 +8776,7 @@
       <c r="I34" t="n">
         <v>3.99</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="K34" t="n">
@@ -2017,13 +8789,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -2050,7 +8822,7 @@
       <c r="I35" t="n">
         <v>4</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="K35" t="n">
@@ -2063,13 +8835,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -2096,7 +8868,7 @@
       <c r="I36" t="n">
         <v>4.06</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="K36" t="n">
@@ -2109,13 +8881,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -2142,7 +8914,7 @@
       <c r="I37" t="n">
         <v>3.87</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="K37" t="n">
@@ -2155,13 +8927,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -2188,7 +8960,7 @@
       <c r="I38" t="n">
         <v>4.1</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="K38" t="n">
@@ -2201,13 +8973,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -2234,7 +9006,7 @@
       <c r="I39" t="n">
         <v>4.06</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="K39" t="n">
@@ -2247,13 +9019,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -2280,7 +9052,7 @@
       <c r="I40" t="n">
         <v>3.969999999999999</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K40" t="n">
@@ -2293,13 +9065,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -2326,7 +9098,7 @@
       <c r="I41" t="n">
         <v>4.26</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="K41" t="n">
@@ -2339,13 +9111,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -2372,7 +9144,7 @@
       <c r="I42" t="n">
         <v>4.28</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="K42" t="n">
@@ -2385,13 +9157,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -2418,7 +9190,7 @@
       <c r="I43" t="n">
         <v>4.52</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="K43" t="n">
@@ -2431,13 +9203,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -2464,7 +9236,7 @@
       <c r="I44" t="n">
         <v>4.84</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="K44" t="n">
@@ -2477,13 +9249,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -2510,7 +9282,7 @@
       <c r="I45" t="n">
         <v>4.630000000000001</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="K45" t="n">
@@ -2523,13 +9295,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -2556,7 +9328,7 @@
       <c r="I46" t="n">
         <v>4.05</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="K46" t="n">
@@ -2569,13 +9341,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -2602,7 +9374,7 @@
       <c r="I47" t="n">
         <v>2.86</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="K47" t="n">
@@ -2615,13 +9387,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -2648,7 +9420,7 @@
       <c r="I48" t="n">
         <v>0.8999999999999999</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="K48" t="n">
@@ -2661,13 +9433,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -2694,7 +9466,7 @@
       <c r="I49" t="n">
         <v>0.3999999999999999</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="K49" t="n">
@@ -2707,13 +9479,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -2740,7 +9512,7 @@
       <c r="I50" t="n">
         <v>0.41</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="K50" t="n">
@@ -2753,13 +9525,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -2786,7 +9558,7 @@
       <c r="I51" t="n">
         <v>1.45</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K51" t="n">
@@ -2799,13 +9571,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -2832,7 +9604,7 @@
       <c r="I52" t="n">
         <v>3.49</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K52" t="n">
@@ -2845,13 +9617,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -2878,7 +9650,7 @@
       <c r="I53" t="n">
         <v>4.24</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="K53" t="n">
@@ -2891,13 +9663,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -2924,7 +9696,7 @@
       <c r="I54" t="n">
         <v>4.950000000000001</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K54" t="n">
@@ -2937,13 +9709,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -2970,7 +9742,7 @@
       <c r="I55" t="n">
         <v>4.78</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="K55" t="n">
@@ -2983,13 +9755,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -3016,7 +9788,7 @@
       <c r="I56" t="n">
         <v>4.140000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="K56" t="n">
@@ -3029,13 +9801,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -3062,7 +9834,7 @@
       <c r="I57" t="n">
         <v>3.82</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="K57" t="n">
@@ -3075,13 +9847,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -3108,7 +9880,7 @@
       <c r="I58" t="n">
         <v>3.14</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="K58" t="n">
@@ -3121,13 +9893,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -3154,7 +9926,7 @@
       <c r="I59" t="n">
         <v>3.49</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K59" t="n">
@@ -3167,13 +9939,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -3200,7 +9972,7 @@
       <c r="I60" t="n">
         <v>4</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="K60" t="n">
@@ -3213,13 +9985,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -3246,7 +10018,7 @@
       <c r="I61" t="n">
         <v>4.63</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K61" t="n">
@@ -3259,13 +10031,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -3292,7 +10064,7 @@
       <c r="I62" t="n">
         <v>4.83</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="K62" t="n">
@@ -3305,13 +10077,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -3338,7 +10110,7 @@
       <c r="I63" t="n">
         <v>4.8</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K63" t="n">
@@ -3351,13 +10123,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -3384,7 +10156,7 @@
       <c r="I64" t="n">
         <v>4.88</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K64" t="n">
@@ -3397,13 +10169,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -3430,7 +10202,7 @@
       <c r="I65" t="n">
         <v>4.82</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K65" t="n">
@@ -3443,13 +10215,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -3476,7 +10248,7 @@
       <c r="I66" t="n">
         <v>5.37</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="K66" t="n">
@@ -3489,13 +10261,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -3522,7 +10294,7 @@
       <c r="I67" t="n">
         <v>5.56</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="K67" t="n">
@@ -3535,13 +10307,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -3568,7 +10340,7 @@
       <c r="I68" t="n">
         <v>5.83</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K68" t="n">
@@ -3581,13 +10353,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -3614,7 +10386,7 @@
       <c r="I69" t="n">
         <v>6.07</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K69" t="n">
@@ -3627,13 +10399,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -3660,7 +10432,7 @@
       <c r="I70" t="n">
         <v>6.26</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="K70" t="n">
@@ -3673,13 +10445,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -3706,7 +10478,7 @@
       <c r="I71" t="n">
         <v>6.47</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K71" t="n">
@@ -3719,13 +10491,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46231</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -3752,7 +10524,7 @@
       <c r="I72" t="n">
         <v>6.869999999999999</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46231</v>
       </c>
       <c r="K72" t="n">
@@ -3789,52 +10561,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="C2" t="n">
@@ -3863,10 +10635,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -3895,10 +10667,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39844</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -3927,10 +10699,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -3959,10 +10731,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C6" t="n">
@@ -3991,10 +10763,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -4023,10 +10795,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -4055,10 +10827,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C9" t="n">
@@ -4087,10 +10859,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -4119,10 +10891,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="C11" t="n">
@@ -4151,10 +10923,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40967</v>
       </c>
       <c r="C12" t="n">
@@ -4183,10 +10955,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C13" t="n">
@@ -4215,10 +10987,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C14" t="n">
@@ -4247,10 +11019,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C15" t="n">
@@ -4279,10 +11051,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="C16" t="n">
@@ -4311,10 +11083,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41402</v>
       </c>
       <c r="C17" t="n">
@@ -4343,10 +11115,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C18" t="n">
@@ -4375,10 +11147,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="C19" t="n">
@@ -4407,10 +11179,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="C20" t="n">
@@ -4439,10 +11211,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="C21" t="n">
@@ -4471,10 +11243,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="C22" t="n">
@@ -4503,10 +11275,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="C23" t="n">
@@ -4535,10 +11307,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42034</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C24" t="n">
@@ -4567,10 +11339,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C25" t="n">
@@ -4599,10 +11371,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C26" t="n">
@@ -4631,10 +11403,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C27" t="n">
@@ -4663,10 +11435,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="C28" t="n">
@@ -4695,10 +11467,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C29" t="n">
@@ -4727,10 +11499,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -4759,10 +11531,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42668</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C31" t="n">
@@ -4791,10 +11563,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42783</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="C32" t="n">
@@ -4823,10 +11595,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42851</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="C33" t="n">
@@ -4855,10 +11627,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42942</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C34" t="n">
@@ -4887,10 +11659,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43033</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="C35" t="n">
@@ -4919,10 +11691,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43151</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="C36" t="n">
@@ -4951,10 +11723,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43215</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C37" t="n">
@@ -4983,10 +11755,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43306</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C38" t="n">
@@ -5015,10 +11787,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43397</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="C39" t="n">
@@ -5047,10 +11819,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43514</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43523</v>
       </c>
       <c r="C40" t="n">
@@ -5079,10 +11851,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43579</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C41" t="n">
@@ -5111,10 +11883,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43670</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="C42" t="n">
@@ -5143,10 +11915,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43761</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C43" t="n">
@@ -5175,10 +11947,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43879</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="C44" t="n">
@@ -5207,10 +11979,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43945</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C45" t="n">
@@ -5239,10 +12011,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44036</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="C46" t="n">
@@ -5271,10 +12043,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="C47" t="n">
@@ -5303,10 +12075,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44243</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="C48" t="n">
@@ -5335,10 +12107,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44308</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C49" t="n">
@@ -5367,10 +12139,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44396</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C50" t="n">
@@ -5399,10 +12171,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44490</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="C51" t="n">
@@ -5431,10 +12203,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44603</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="C52" t="n">
@@ -5463,10 +12235,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44673</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="C53" t="n">
@@ -5495,10 +12267,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44763</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="C54" t="n">
@@ -5527,10 +12299,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44854</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="C55" t="n">
@@ -5559,10 +12331,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44967</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="C56" t="n">
@@ -5591,10 +12363,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45037</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C57" t="n">
@@ -5623,10 +12395,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45219</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C58" t="n">
@@ -5655,10 +12427,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45331</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="C59" t="n">
@@ -5687,10 +12459,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45405</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C60" t="n">
@@ -5719,10 +12491,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45496</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C61" t="n">
@@ -5751,10 +12523,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45587</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C62" t="n">
@@ -5783,10 +12555,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45702</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="C63" t="n">
@@ -5815,10 +12587,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45764</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C64" t="n">
@@ -5847,10 +12619,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45861</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C65" t="n">
@@ -5879,10 +12651,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45952</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C66" t="n">
@@ -5911,10 +12683,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46066</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46077</v>
       </c>
       <c r="C67" t="n">
@@ -5943,10 +12715,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C68" t="n">
@@ -5975,10 +12747,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46220</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46231</v>
       </c>
       <c r="C69" t="n">
@@ -6025,12 +12797,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -6166,7 +12938,11 @@
           <t>Splits aplicados</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1977-06-20 2:1; 1988-07-01 1.5:1; 1989-07-24 2:1; 1993-06-29 2:1; 1997-10-14 2:1; 2006-08-14 2:1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6199,7 +12975,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17">
@@ -6208,7 +12984,11 @@
           <t>Rango precio</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2006-01 a 2026-09</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6217,7 +12997,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19">
@@ -6226,7 +13006,11 @@
           <t>Rango P/E</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2011-02 a 2026-09</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6235,7 +13019,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21">
@@ -6244,7 +13028,11 @@
           <t>Rango market cap</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2009-08 a 2026-09</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6252,11 +13040,7 @@
           <t>Error Yahoo</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Yahoo Finance regresó datos vacíos (ticker deslistado, renombrado o mal escrito)</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/salidas/empresas/WFC.xlsx
+++ b/salidas/empresas/WFC.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>17.76022720336914</v>
+        <v>17.76022911071777</v>
       </c>
       <c r="C2" t="n">
         <v>31.18000030517578</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>18.43801307678223</v>
+        <v>18.43801879882812</v>
       </c>
       <c r="C3" t="n">
         <v>32.09999847412109</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>18.34323501586914</v>
+        <v>18.34324073791504</v>
       </c>
       <c r="C4" t="n">
         <v>31.93499946594238</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>19.72752571105957</v>
+        <v>19.7275218963623</v>
       </c>
       <c r="C5" t="n">
         <v>34.34500122070312</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>19.20835304260254</v>
+        <v>19.20835876464844</v>
       </c>
       <c r="C6" t="n">
         <v>33.18500137329102</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>19.41383934020996</v>
+        <v>19.41384506225586</v>
       </c>
       <c r="C7" t="n">
         <v>33.54000091552734</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>20.93614959716797</v>
+        <v>20.9361515045166</v>
       </c>
       <c r="C8" t="n">
         <v>36.16999816894531</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>20.27071189880371</v>
+        <v>20.27070617675781</v>
       </c>
       <c r="C9" t="n">
         <v>34.75</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>21.1048698425293</v>
+        <v>21.1048641204834</v>
       </c>
       <c r="C10" t="n">
         <v>36.18000030517578</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>21.16903114318848</v>
+        <v>21.16903686523438</v>
       </c>
       <c r="C11" t="n">
         <v>36.29000091552734</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>20.71637916564941</v>
+        <v>20.71638298034668</v>
       </c>
       <c r="C12" t="n">
         <v>35.2400016784668</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.90449714660645</v>
+        <v>20.90449333190918</v>
       </c>
       <c r="C13" t="n">
         <v>35.56000137329102</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>20.55928039550781</v>
+        <v>20.55928993225098</v>
       </c>
       <c r="C15" t="n">
         <v>34.70000076293945</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>20.39932441711426</v>
+        <v>20.39931106567383</v>
       </c>
       <c r="C16" t="n">
         <v>34.43000030517578</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>21.26433753967285</v>
+        <v>21.26433944702148</v>
       </c>
       <c r="C17" t="n">
         <v>35.88999938964844</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>21.55026245117188</v>
+        <v>21.55026817321777</v>
       </c>
       <c r="C18" t="n">
         <v>36.09000015258789</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>21.00089836120605</v>
+        <v>21.00090217590332</v>
       </c>
       <c r="C19" t="n">
         <v>35.16999816894531</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>20.16493606567383</v>
+        <v>20.1649284362793</v>
       </c>
       <c r="C20" t="n">
         <v>33.77000045776367</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>22.01457214355469</v>
+        <v>22.01457786560059</v>
       </c>
       <c r="C21" t="n">
         <v>36.54000091552734</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>21.46029281616211</v>
+        <v>21.46028900146484</v>
       </c>
       <c r="C22" t="n">
         <v>35.61999893188477</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>20.49029350280762</v>
+        <v>20.49030303955078</v>
       </c>
       <c r="C23" t="n">
         <v>34.0099983215332</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>19.72395324707031</v>
+        <v>19.72394752502441</v>
       </c>
       <c r="C24" t="n">
         <v>32.43000030517578</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>18.36157989501953</v>
+        <v>18.36157417297363</v>
       </c>
       <c r="C25" t="n">
         <v>30.19000053405762</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>20.72749328613281</v>
+        <v>20.72747993469238</v>
       </c>
       <c r="C26" t="n">
         <v>34.08000183105469</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>17.96043395996094</v>
+        <v>17.96043968200684</v>
       </c>
       <c r="C27" t="n">
         <v>29.22999954223633</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>17.88056182861328</v>
+        <v>17.88055801391602</v>
       </c>
       <c r="C28" t="n">
         <v>29.10000038146973</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>18.27995300292969</v>
+        <v>18.27994537353516</v>
       </c>
       <c r="C29" t="n">
         <v>29.75</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>17.11006546020508</v>
+        <v>17.11007308959961</v>
       </c>
       <c r="C30" t="n">
         <v>27.56999969482422</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>14.73936462402344</v>
+        <v>14.73936080932617</v>
       </c>
       <c r="C31" t="n">
         <v>23.75</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>18.78570365905762</v>
+        <v>18.78570747375488</v>
       </c>
       <c r="C32" t="n">
         <v>30.27000045776367</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>18.99042129516602</v>
+        <v>18.99041938781738</v>
       </c>
       <c r="C33" t="n">
         <v>30.27000045776367</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>23.54510116577148</v>
+        <v>23.54510498046875</v>
       </c>
       <c r="C34" t="n">
         <v>37.52999877929688</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>21.36186981201172</v>
+        <v>21.36187553405762</v>
       </c>
       <c r="C35" t="n">
         <v>34.04999923706055</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>18.30188369750977</v>
+        <v>18.30188751220703</v>
       </c>
       <c r="C36" t="n">
         <v>28.88999938964844</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>18.67565155029297</v>
+        <v>18.6756477355957</v>
       </c>
       <c r="C37" t="n">
         <v>29.47999954223633</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>11.9731969833374</v>
+        <v>11.97319793701172</v>
       </c>
       <c r="C38" t="n">
         <v>18.89999961853027</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>7.808657169342041</v>
+        <v>7.808655261993408</v>
       </c>
       <c r="C39" t="n">
         <v>12.10000038146973</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>12.91332244873047</v>
+        <v>12.91332149505615</v>
       </c>
       <c r="C41" t="n">
         <v>20.01000022888184</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>16.49169731140137</v>
+        <v>16.4916934967041</v>
       </c>
       <c r="C42" t="n">
         <v>25.5</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.68974113464355</v>
+        <v>15.68974781036377</v>
       </c>
       <c r="C43" t="n">
         <v>24.26000022888184</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>15.81909084320068</v>
+        <v>15.81909656524658</v>
       </c>
       <c r="C44" t="n">
         <v>24.45999908447266</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>17.83167457580566</v>
+        <v>17.83168029785156</v>
       </c>
       <c r="C45" t="n">
         <v>27.52000045776367</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>17.83167457580566</v>
+        <v>17.83168029785156</v>
       </c>
       <c r="C47" t="n">
         <v>27.52000045776367</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.2014217376709</v>
+        <v>18.20141983032227</v>
       </c>
       <c r="C48" t="n">
         <v>28.04000091552734</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>17.77791595458984</v>
+        <v>17.77790832519531</v>
       </c>
       <c r="C51" t="n">
         <v>27.34000015258789</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>20.23586845397949</v>
+        <v>20.23586082458496</v>
       </c>
       <c r="C52" t="n">
         <v>31.1200008392334</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>21.52987480163574</v>
+        <v>21.52987289428711</v>
       </c>
       <c r="C53" t="n">
         <v>33.11000061035156</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>18.68411445617676</v>
+        <v>18.68411636352539</v>
       </c>
       <c r="C54" t="n">
         <v>28.69000053405762</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>16.67177581787109</v>
+        <v>16.67178153991699</v>
       </c>
       <c r="C55" t="n">
         <v>25.60000038146973</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>18.05891990661621</v>
+        <v>18.05892181396484</v>
       </c>
       <c r="C56" t="n">
         <v>27.72999954223633</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>15.36405658721924</v>
+        <v>15.36405563354492</v>
       </c>
       <c r="C57" t="n">
         <v>23.54999923706055</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>16.3883228302002</v>
+        <v>16.3883171081543</v>
       </c>
       <c r="C58" t="n">
         <v>25.1200008392334</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.25691986083984</v>
+        <v>20.25691604614258</v>
       </c>
       <c r="C61" t="n">
         <v>30.98999977111816</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>20.80489540100098</v>
+        <v>20.80489730834961</v>
       </c>
       <c r="C64" t="n">
         <v>31.70999908447266</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>19.09904670715332</v>
+        <v>19.09903717041016</v>
       </c>
       <c r="C65" t="n">
         <v>29.11000061035156</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>18.68952941894531</v>
+        <v>18.68953132629395</v>
       </c>
       <c r="C66" t="n">
         <v>28.3700008392334</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>18.40625381469727</v>
+        <v>18.40624809265137</v>
       </c>
       <c r="C68" t="n">
         <v>27.94000053405762</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>15.96018981933594</v>
+        <v>15.9601879119873</v>
       </c>
       <c r="C70" t="n">
         <v>24.1200008392334</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>17.14463043212891</v>
+        <v>17.14463424682617</v>
       </c>
       <c r="C71" t="n">
         <v>25.90999984741211</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>18.32521438598633</v>
+        <v>18.32521057128906</v>
       </c>
       <c r="C73" t="n">
         <v>27.55999946594238</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>19.42232704162598</v>
+        <v>19.42232513427734</v>
       </c>
       <c r="C74" t="n">
         <v>29.20999908447266</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>20.89118576049805</v>
+        <v>20.89118766784668</v>
       </c>
       <c r="C75" t="n">
         <v>31.29000091552734</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>22.86123085021973</v>
+        <v>22.86122894287109</v>
       </c>
       <c r="C76" t="n">
         <v>34.13999938964844</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>22.53793525695801</v>
+        <v>22.53793334960938</v>
       </c>
       <c r="C79" t="n">
         <v>33.43999862670898</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>22.78730392456055</v>
+        <v>22.78731155395508</v>
       </c>
       <c r="C80" t="n">
         <v>33.81000137329102</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>22.8544864654541</v>
+        <v>22.8544807434082</v>
       </c>
       <c r="C83" t="n">
         <v>33.68999862670898</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>22.53766059875488</v>
+        <v>22.53766632080078</v>
       </c>
       <c r="C84" t="n">
         <v>33.0099983215332</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>23.33647918701172</v>
+        <v>23.33648109436035</v>
       </c>
       <c r="C85" t="n">
         <v>34.18000030517578</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>23.95003318786621</v>
+        <v>23.95003509521484</v>
       </c>
       <c r="C86" t="n">
         <v>34.83000183105469</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>24.1219367980957</v>
+        <v>24.1219425201416</v>
       </c>
       <c r="C87" t="n">
         <v>35.08000183105469</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>25.43530654907227</v>
+        <v>25.43531608581543</v>
       </c>
       <c r="C88" t="n">
         <v>36.9900016784668</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>26.11605262756348</v>
+        <v>26.11605072021484</v>
       </c>
       <c r="C89" t="n">
         <v>37.97999954223633</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>28.10280609130859</v>
+        <v>28.10281753540039</v>
       </c>
       <c r="C90" t="n">
         <v>40.54999923706055</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>28.60180282592773</v>
+        <v>28.60180473327637</v>
       </c>
       <c r="C91" t="n">
         <v>41.27000045776367</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>30.14727020263672</v>
+        <v>30.14727210998535</v>
       </c>
       <c r="C92" t="n">
         <v>43.5</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>28.66543769836426</v>
+        <v>28.66544532775879</v>
       </c>
       <c r="C93" t="n">
         <v>41.08000183105469</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>28.83290672302246</v>
+        <v>28.83290863037109</v>
       </c>
       <c r="C94" t="n">
         <v>41.31999969482422</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>29.78888702392578</v>
+        <v>29.78889083862305</v>
       </c>
       <c r="C95" t="n">
         <v>42.68999862670898</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>30.93464660644531</v>
+        <v>30.93464851379395</v>
       </c>
       <c r="C96" t="n">
         <v>44.02000045776367</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>31.90442657470703</v>
+        <v>31.9044361114502</v>
       </c>
       <c r="C97" t="n">
         <v>45.40000152587891</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>31.86226654052734</v>
+        <v>31.86227035522461</v>
       </c>
       <c r="C98" t="n">
         <v>45.34000015258789</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>32.84130096435547</v>
+        <v>32.84128952026367</v>
       </c>
       <c r="C99" t="n">
         <v>46.41999816894531</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>35.19012451171875</v>
+        <v>35.19012832641602</v>
       </c>
       <c r="C100" t="n">
         <v>49.7400016784668</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>35.1193962097168</v>
+        <v>35.119384765625</v>
       </c>
       <c r="C101" t="n">
         <v>49.63999938964844</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>36.18390274047852</v>
+        <v>36.18389892578125</v>
       </c>
       <c r="C102" t="n">
         <v>50.77999877929688</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>37.45226669311523</v>
+        <v>37.45227432250977</v>
       </c>
       <c r="C103" t="n">
         <v>52.56000137329102</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>36.26940536499023</v>
+        <v>36.26940155029297</v>
       </c>
       <c r="C104" t="n">
         <v>50.90000152587891</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>36.91051864624023</v>
+        <v>36.9105110168457</v>
       </c>
       <c r="C105" t="n">
         <v>51.43999862670898</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>37.21904754638672</v>
+        <v>37.21905136108398</v>
       </c>
       <c r="C106" t="n">
         <v>51.86999893188477</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>38.09445953369141</v>
+        <v>38.09446334838867</v>
       </c>
       <c r="C107" t="n">
         <v>53.09000015258789</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>39.35037612915039</v>
+        <v>39.35039520263672</v>
       </c>
       <c r="C108" t="n">
         <v>54.47999954223633</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>39.59596633911133</v>
+        <v>39.59595489501953</v>
       </c>
       <c r="C109" t="n">
         <v>54.81999969482422</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>37.50132751464844</v>
+        <v>37.5013313293457</v>
       </c>
       <c r="C110" t="n">
         <v>51.91999816894531</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>39.83514404296875</v>
+        <v>39.83513641357422</v>
       </c>
       <c r="C111" t="n">
         <v>54.79000091552734</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>40.06052780151367</v>
+        <v>40.06052398681641</v>
       </c>
       <c r="C113" t="n">
         <v>55.09999847412109</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>40.96147155761719</v>
+        <v>40.96146774291992</v>
       </c>
       <c r="C114" t="n">
         <v>55.95999908447266</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>41.16641998291016</v>
+        <v>41.16642761230469</v>
       </c>
       <c r="C115" t="n">
         <v>56.2400016784668</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>42.35953903198242</v>
+        <v>42.35955047607422</v>
       </c>
       <c r="C116" t="n">
         <v>57.86999893188477</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>39.29121398925781</v>
+        <v>39.29120254516602</v>
       </c>
       <c r="C117" t="n">
         <v>53.33000183105469</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>37.83243179321289</v>
+        <v>37.83242797851562</v>
       </c>
       <c r="C118" t="n">
         <v>51.34999847412109</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>39.88798141479492</v>
+        <v>39.88797378540039</v>
       </c>
       <c r="C119" t="n">
         <v>54.13999938964844</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>40.87429046630859</v>
+        <v>40.87429428100586</v>
       </c>
       <c r="C120" t="n">
         <v>55.09999847412109</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>40.32536697387695</v>
+        <v>40.32535171508789</v>
       </c>
       <c r="C121" t="n">
         <v>54.36000061035156</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>37.26162719726562</v>
+        <v>37.26163482666016</v>
       </c>
       <c r="C122" t="n">
         <v>50.22999954223633</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>35.07558441162109</v>
+        <v>35.07557678222656</v>
       </c>
       <c r="C123" t="n">
         <v>46.91999816894531</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>36.15206146240234</v>
+        <v>36.15206527709961</v>
       </c>
       <c r="C124" t="n">
         <v>48.36000061035156</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>37.36312484741211</v>
+        <v>37.36311721801758</v>
       </c>
       <c r="C125" t="n">
         <v>49.97999954223633</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>38.20668029785156</v>
+        <v>38.20668792724609</v>
       </c>
       <c r="C126" t="n">
         <v>50.72000122070312</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>35.65304565429688</v>
+        <v>35.65304946899414</v>
       </c>
       <c r="C127" t="n">
         <v>47.33000183105469</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>38.57423782348633</v>
+        <v>38.57424545288086</v>
       </c>
       <c r="C129" t="n">
         <v>50.79999923706055</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>33.62338256835938</v>
+        <v>33.62337493896484</v>
       </c>
       <c r="C130" t="n">
         <v>44.27999877929688</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>34.93703079223633</v>
+        <v>34.93703842163086</v>
       </c>
       <c r="C131" t="n">
         <v>46.0099983215332</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>40.51882934570312</v>
+        <v>40.51883316040039</v>
       </c>
       <c r="C132" t="n">
         <v>52.91999816894531</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>42.19563674926758</v>
+        <v>42.19563293457031</v>
       </c>
       <c r="C133" t="n">
         <v>55.11000061035156</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>43.12974166870117</v>
+        <v>43.1297492980957</v>
       </c>
       <c r="C134" t="n">
         <v>56.33000183105469</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>44.61749267578125</v>
+        <v>44.61750793457031</v>
       </c>
       <c r="C135" t="n">
         <v>57.88000106811523</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>42.90618515014648</v>
+        <v>42.90620040893555</v>
       </c>
       <c r="C136" t="n">
         <v>55.65999984741211</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>41.50322723388672</v>
+        <v>41.50323104858398</v>
       </c>
       <c r="C137" t="n">
         <v>53.84000015258789</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>39.69847869873047</v>
+        <v>39.698486328125</v>
       </c>
       <c r="C138" t="n">
         <v>51.13999938964844</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>43.01315307617188</v>
+        <v>43.01316452026367</v>
       </c>
       <c r="C139" t="n">
         <v>55.40999984741211</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>41.87203979492188</v>
+        <v>41.87204360961914</v>
       </c>
       <c r="C140" t="n">
         <v>53.93999862670898</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>39.93212509155273</v>
+        <v>39.9321174621582</v>
       </c>
       <c r="C141" t="n">
         <v>51.06999969482422</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>43.12231063842773</v>
+        <v>43.122314453125</v>
       </c>
       <c r="C142" t="n">
         <v>55.15000152587891</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>43.89640808105469</v>
+        <v>43.89639282226562</v>
       </c>
       <c r="C143" t="n">
         <v>56.13999938964844</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>44.46292877197266</v>
+        <v>44.46293640136719</v>
       </c>
       <c r="C144" t="n">
         <v>56.47000122070312</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>47.7698860168457</v>
+        <v>47.76990509033203</v>
       </c>
       <c r="C145" t="n">
         <v>60.66999816894531</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>51.79337310791016</v>
+        <v>51.79336166381836</v>
       </c>
       <c r="C146" t="n">
         <v>65.77999877929688</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>41.51231384277344</v>
+        <v>41.5123176574707</v>
       </c>
       <c r="C148" t="n">
         <v>52.40999984741211</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>41.15587997436523</v>
+        <v>41.15589141845703</v>
       </c>
       <c r="C149" t="n">
         <v>51.95999908447266</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>43.08575057983398</v>
+        <v>43.08575439453125</v>
       </c>
       <c r="C150" t="n">
         <v>53.9900016784668</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>44.24290084838867</v>
+        <v>44.24289703369141</v>
       </c>
       <c r="C151" t="n">
         <v>55.43999862670898</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>45.71926116943359</v>
+        <v>45.7192497253418</v>
       </c>
       <c r="C152" t="n">
         <v>57.29000091552734</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>47.01043319702148</v>
+        <v>47.01043701171875</v>
       </c>
       <c r="C153" t="n">
         <v>58.47999954223633</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>42.25152587890625</v>
+        <v>42.25151824951172</v>
       </c>
       <c r="C154" t="n">
         <v>52.56000137329102</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>42.79011154174805</v>
+        <v>42.79010391235352</v>
       </c>
       <c r="C155" t="n">
         <v>53.22999954223633</v>
@@ -4462,7 +4462,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>43.98717880249023</v>
+        <v>43.98719024658203</v>
       </c>
       <c r="C156" t="n">
         <v>54.27999877929688</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>39.99477386474609</v>
+        <v>39.99477767944336</v>
       </c>
       <c r="C158" t="n">
         <v>48.90999984741211</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>40.796142578125</v>
+        <v>40.79614639282227</v>
       </c>
       <c r="C159" t="n">
         <v>49.88999938964844</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>39.5123176574707</v>
+        <v>39.51232528686523</v>
       </c>
       <c r="C160" t="n">
         <v>48.31999969482422</v>
@@ -4607,7 +4607,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>39.58591461181641</v>
+        <v>39.58591842651367</v>
       </c>
       <c r="C161" t="n">
         <v>48.40999984741211</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>39.96859359741211</v>
+        <v>39.96858215332031</v>
       </c>
       <c r="C164" t="n">
         <v>48.40999984741211</v>
@@ -4723,7 +4723,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>38.88232803344727</v>
+        <v>38.88230895996094</v>
       </c>
       <c r="C165" t="n">
         <v>46.56999969482422</v>
@@ -4781,7 +4781,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>43.10702514648438</v>
+        <v>43.10701751708984</v>
       </c>
       <c r="C167" t="n">
         <v>51.63000106811523</v>
@@ -4810,7 +4810,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>45.90501403808594</v>
+        <v>45.90500259399414</v>
       </c>
       <c r="C168" t="n">
         <v>54.45999908447266</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>45.34869384765625</v>
+        <v>45.34868240356445</v>
       </c>
       <c r="C169" t="n">
         <v>53.79999923706055</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>39.56631469726562</v>
+        <v>39.56631088256836</v>
       </c>
       <c r="C170" t="n">
         <v>46.93999862670898</v>
@@ -4897,7 +4897,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>34.80035018920898</v>
+        <v>34.80035400390625</v>
       </c>
       <c r="C171" t="n">
         <v>40.84999847412109</v>
@@ -4926,7 +4926,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>24.44969749450684</v>
+        <v>24.44969367980957</v>
       </c>
       <c r="C172" t="n">
         <v>28.70000076293945</v>
@@ -4955,7 +4955,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>24.74786376953125</v>
+        <v>24.74786567687988</v>
       </c>
       <c r="C173" t="n">
         <v>29.04999923706055</v>
@@ -4984,7 +4984,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>23.00813293457031</v>
+        <v>23.00813484191895</v>
       </c>
       <c r="C174" t="n">
         <v>26.46999931335449</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>22.25191688537598</v>
+        <v>22.25192260742188</v>
       </c>
       <c r="C175" t="n">
         <v>25.60000038146973</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>21.07793807983398</v>
+        <v>21.07793617248535</v>
       </c>
       <c r="C177" t="n">
         <v>24.14999961853027</v>
@@ -5100,7 +5100,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>20.51935005187988</v>
+        <v>20.51934814453125</v>
       </c>
       <c r="C178" t="n">
         <v>23.51000022888184</v>
@@ -5158,7 +5158,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>23.9804744720459</v>
+        <v>23.98047256469727</v>
       </c>
       <c r="C180" t="n">
         <v>27.35000038146973</v>
@@ -5187,7 +5187,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>26.46181678771973</v>
+        <v>26.46181869506836</v>
       </c>
       <c r="C181" t="n">
         <v>30.18000030517578</v>
@@ -5216,7 +5216,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>26.19877243041992</v>
+        <v>26.19877815246582</v>
       </c>
       <c r="C182" t="n">
         <v>29.8799991607666</v>
@@ -5245,7 +5245,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>31.81420135498047</v>
+        <v>31.81420516967773</v>
       </c>
       <c r="C183" t="n">
         <v>36.16999816894531</v>
@@ -5274,7 +5274,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>34.36497497558594</v>
+        <v>34.3649787902832</v>
       </c>
       <c r="C184" t="n">
         <v>39.06999969482422</v>
@@ -5303,7 +5303,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>39.62483215332031</v>
+        <v>39.62483978271484</v>
       </c>
       <c r="C185" t="n">
         <v>45.04999923706055</v>
@@ -5332,7 +5332,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>41.18337249755859</v>
+        <v>41.18337631225586</v>
       </c>
       <c r="C186" t="n">
         <v>46.72000122070312</v>
@@ -5361,7 +5361,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>39.9228401184082</v>
+        <v>39.92283630371094</v>
       </c>
       <c r="C187" t="n">
         <v>45.29000091552734</v>
@@ -5419,7 +5419,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>40.45958709716797</v>
+        <v>40.45957946777344</v>
       </c>
       <c r="C189" t="n">
         <v>45.70000076293945</v>
@@ -5448,7 +5448,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>41.08816146850586</v>
+        <v>41.08816909790039</v>
       </c>
       <c r="C190" t="n">
         <v>46.40999984741211</v>
@@ -5477,7 +5477,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>45.29348754882812</v>
+        <v>45.29347610473633</v>
       </c>
       <c r="C191" t="n">
         <v>51.15999984741211</v>
@@ -5506,7 +5506,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>42.46438980102539</v>
+        <v>42.46439361572266</v>
       </c>
       <c r="C192" t="n">
         <v>47.77999877929688</v>
@@ -5535,7 +5535,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>42.64214324951172</v>
+        <v>42.64215087890625</v>
       </c>
       <c r="C193" t="n">
         <v>47.97999954223633</v>
@@ -5564,7 +5564,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>47.81465911865234</v>
+        <v>47.81465530395508</v>
       </c>
       <c r="C194" t="n">
         <v>53.79999923706055</v>
@@ -5593,7 +5593,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>47.64546966552734</v>
+        <v>47.64546585083008</v>
       </c>
       <c r="C195" t="n">
         <v>53.36999893188477</v>
@@ -5622,7 +5622,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>43.26211929321289</v>
+        <v>43.26211547851562</v>
       </c>
       <c r="C196" t="n">
         <v>48.45999908447266</v>
@@ -5651,7 +5651,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>38.95018768310547</v>
+        <v>38.9501953125</v>
       </c>
       <c r="C197" t="n">
         <v>43.63000106811523</v>
@@ -5680,7 +5680,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>41.08402633666992</v>
+        <v>41.08403396606445</v>
       </c>
       <c r="C198" t="n">
         <v>45.77000045776367</v>
@@ -5709,7 +5709,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>35.15974044799805</v>
+        <v>35.15973663330078</v>
       </c>
       <c r="C199" t="n">
         <v>39.16999816894531</v>
@@ -5738,7 +5738,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>39.37855529785156</v>
+        <v>39.37854766845703</v>
       </c>
       <c r="C200" t="n">
         <v>43.86999893188477</v>
@@ -5767,7 +5767,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>39.50496292114258</v>
+        <v>39.50496673583984</v>
       </c>
       <c r="C201" t="n">
         <v>43.70999908447266</v>
@@ -5796,7 +5796,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>36.35071182250977</v>
+        <v>36.35071563720703</v>
       </c>
       <c r="C202" t="n">
         <v>40.22000122070312</v>
@@ -5883,7 +5883,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>37.55812072753906</v>
+        <v>37.55812454223633</v>
       </c>
       <c r="C205" t="n">
         <v>41.29000091552734</v>
@@ -5912,7 +5912,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>42.63378524780273</v>
+        <v>42.6337890625</v>
       </c>
       <c r="C206" t="n">
         <v>46.86999893188477</v>
@@ -5941,7 +5941,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>42.814208984375</v>
+        <v>42.81420516967773</v>
       </c>
       <c r="C207" t="n">
         <v>46.77000045776367</v>
@@ -5970,7 +5970,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>34.21841049194336</v>
+        <v>34.21840667724609</v>
       </c>
       <c r="C208" t="n">
         <v>37.38000106811523</v>
@@ -5999,7 +5999,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>36.38795852661133</v>
+        <v>36.38795471191406</v>
       </c>
       <c r="C209" t="n">
         <v>39.75</v>
@@ -6028,7 +6028,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>36.72795486450195</v>
+        <v>36.72796249389648</v>
       </c>
       <c r="C210" t="n">
         <v>39.81000137329102</v>
@@ -6086,7 +6086,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>42.58634948730469</v>
+        <v>42.58635330200195</v>
       </c>
       <c r="C212" t="n">
         <v>46.15999984741211</v>
@@ -6115,7 +6115,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>38.39132308959961</v>
+        <v>38.39131546020508</v>
       </c>
       <c r="C213" t="n">
         <v>41.29000091552734</v>
@@ -6144,7 +6144,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>37.99149703979492</v>
+        <v>37.99150848388672</v>
       </c>
       <c r="C214" t="n">
         <v>40.86000061035156</v>
@@ -6173,7 +6173,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>36.97802734375</v>
+        <v>36.97802352905273</v>
       </c>
       <c r="C215" t="n">
         <v>39.77000045776367</v>
@@ -6202,7 +6202,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>41.82925415039062</v>
+        <v>41.82925796508789</v>
       </c>
       <c r="C216" t="n">
         <v>44.59000015258789</v>
@@ -6260,7 +6260,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>47.07315444946289</v>
+        <v>47.07316589355469</v>
       </c>
       <c r="C218" t="n">
         <v>50.18000030517578</v>
@@ -6347,7 +6347,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>56.03812789916992</v>
+        <v>56.03812408447266</v>
       </c>
       <c r="C221" t="n">
         <v>59.31999969482422</v>
@@ -6376,7 +6376,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>56.93035507202148</v>
+        <v>56.93035125732422</v>
       </c>
       <c r="C222" t="n">
         <v>59.91999816894531</v>
@@ -6405,7 +6405,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>56.42679214477539</v>
+        <v>56.42678833007812</v>
       </c>
       <c r="C223" t="n">
         <v>59.38999938964844</v>
@@ -6434,7 +6434,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>56.3792839050293</v>
+        <v>56.37929153442383</v>
       </c>
       <c r="C224" t="n">
         <v>59.34000015258789</v>
@@ -6463,7 +6463,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>55.97708511352539</v>
+        <v>55.97708129882812</v>
       </c>
       <c r="C225" t="n">
         <v>58.47000122070312</v>
@@ -6492,7 +6492,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>54.08150482177734</v>
+        <v>54.08151245117188</v>
       </c>
       <c r="C226" t="n">
         <v>56.4900016784668</v>
@@ -6521,7 +6521,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>62.15208053588867</v>
+        <v>62.15208435058594</v>
       </c>
       <c r="C227" t="n">
         <v>64.91999816894531</v>
@@ -6579,7 +6579,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>67.63272094726562</v>
+        <v>67.63272857666016</v>
       </c>
       <c r="C229" t="n">
         <v>70.23999786376953</v>
@@ -6608,7 +6608,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>75.875</v>
+        <v>75.87499237060547</v>
       </c>
       <c r="C230" t="n">
         <v>78.80000305175781</v>
@@ -6637,7 +6637,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>75.78512573242188</v>
+        <v>75.78511810302734</v>
       </c>
       <c r="C231" t="n">
         <v>78.31999969482422</v>
@@ -6666,7 +6666,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>69.46646118164062</v>
+        <v>69.46646881103516</v>
       </c>
       <c r="C232" t="n">
         <v>71.79000091552734</v>
@@ -6753,7 +6753,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>77.95219421386719</v>
+        <v>77.95218658447266</v>
       </c>
       <c r="C235" t="n">
         <v>80.12000274658203</v>
@@ -6840,7 +6840,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>82.03116607666016</v>
+        <v>82.03117370605469</v>
       </c>
       <c r="C238" t="n">
         <v>83.81999969482422</v>
@@ -6869,7 +6869,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>85.11395263671875</v>
+        <v>85.11394500732422</v>
       </c>
       <c r="C239" t="n">
         <v>86.97000122070312</v>
@@ -6898,7 +6898,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>84.45958709716797</v>
+        <v>84.45957946777344</v>
       </c>
       <c r="C240" t="n">
         <v>85.84999847412109</v>
@@ -6927,7 +6927,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>91.69053649902344</v>
+        <v>91.69054412841797</v>
       </c>
       <c r="C241" t="n">
         <v>93.19999694824219</v>
@@ -7043,7 +7043,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>81.29581451416016</v>
+        <v>81.29582214355469</v>
       </c>
       <c r="C245" t="n">
         <v>82.23000335693359</v>
